--- a/data/trending_integrated_20261030_10.xlsx
+++ b/data/trending_integrated_20261030_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18810</v>
+        <v>18220</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+109.00%</t>
+          <t>'+102.44%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F2" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G2" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>195362841285</v>
+        <v>207787144850</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>단타 종목으로 인식. 신규주 폐가망신주 경고 및 크리에이츠와의 비교.</t>
+          <t>신규 상장주의 높은 변동성과 단기 급등락 반복. 크리에이츠와의 이익 비교 및 유통 물량 적은 점을 들어 장기 보유 시 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규주', '단타', '크리에이츠']</t>
+          <t>['신규상장주', '변동성', '유통물량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,79 +655,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12770</v>
+        <v>8860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.02%</t>
+          <t>'+15.06%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>0.37</v>
       </c>
       <c r="E3" t="n">
-        <v>198</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>132</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>552</v>
+        <v>70</v>
       </c>
       <c r="H3" t="n">
-        <v>15.04</v>
+        <v>13.29</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11200</v>
+        <v>7700</v>
       </c>
       <c r="K3" t="n">
-        <v>13500</v>
+        <v>9360</v>
       </c>
       <c r="L3" t="n">
-        <v>13710</v>
+        <v>9500</v>
       </c>
       <c r="M3" t="n">
-        <v>12100</v>
+        <v>8610</v>
       </c>
       <c r="N3" t="n">
-        <v>15.08</v>
+        <v>12.92</v>
       </c>
       <c r="O3" t="n">
-        <v>26530512470</v>
+        <v>5513696590</v>
       </c>
       <c r="P3" t="n">
-        <v>18960</v>
+        <v>13670</v>
       </c>
       <c r="Q3" t="n">
-        <v>5730</v>
+        <v>7060</v>
       </c>
       <c r="R3" t="n">
-        <v>-260000</v>
+        <v>-73000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 성공. 100억 달러 규모의 백색 LED 시장 석권 기대. 기술 개발 기반 주가 상승 및 공매도 세력과의 경쟁 전망.</t>
+          <t>3상 성공 가능성에도 불구하고 역류성 식도염 시장 규모 제한 및 경쟁 심화 우려. 외인/기관 매도세로 주가 하락 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['백색 LED', '희토류', '시장 석권']</t>
+          <t>['3상 성공', '시장 규모', '경쟁']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8770</v>
+        <v>12760</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.90%</t>
+          <t>'+13.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.37</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="G4" t="n">
-        <v>66</v>
+        <v>599</v>
       </c>
       <c r="H4" t="n">
-        <v>13.29</v>
+        <v>15.04</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7700</v>
+        <v>11200</v>
       </c>
       <c r="K4" t="n">
-        <v>9360</v>
+        <v>13500</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>13710</v>
       </c>
       <c r="M4" t="n">
-        <v>8610</v>
+        <v>12100</v>
       </c>
       <c r="N4" t="n">
-        <v>12.92</v>
+        <v>15.08</v>
       </c>
       <c r="O4" t="n">
-        <v>5254772035</v>
+        <v>31020676580</v>
       </c>
       <c r="P4" t="n">
-        <v>13670</v>
+        <v>18960</v>
       </c>
       <c r="Q4" t="n">
-        <v>7060</v>
+        <v>5730</v>
       </c>
       <c r="R4" t="n">
-        <v>-73000</v>
+        <v>-260000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3상 성공에도 낮은 시장 규모 및 개미 꼬시기 의혹. 역류성 식도염 치료제 관련 내용.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 성공. 100억 달러 시장 석권 기대감. 2연상 기록, 공매도 세력 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['3상 성공', '시장 규모', '역류성 식도염']</t>
+          <t>['백색LED', '희토류', '기술개발']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
@@ -854,13 +854,13 @@
         <v>-0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>4.35</v>
       </c>
       <c r="O5" t="n">
-        <v>53341421080</v>
+        <v>55081952545</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>라온시큐어, 11월 양자관련법 시행 기대감과 함께 보안주로서의 긍정적 전망. 다만, 일부 부정적 의견도 존재.</t>
+          <t>11월 양자 관련법 시행 시 최대 수혜 기대. 보안주로서의 성장 가능성 언급. 거래량 대비 주가 하락에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '수혜주']</t>
+          <t>['양자보안', '보안주', '기술력']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16020</v>
+        <v>6870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.94%</t>
+          <t>'+10.10%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14980</v>
+        <v>6240</v>
       </c>
       <c r="K6" t="n">
-        <v>14980</v>
+        <v>6700</v>
       </c>
       <c r="L6" t="n">
-        <v>16050</v>
+        <v>7670</v>
       </c>
       <c r="M6" t="n">
-        <v>14610</v>
+        <v>6330</v>
       </c>
       <c r="N6" t="n">
-        <v>8.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>28481584935</v>
+        <v>12222277855</v>
       </c>
       <c r="P6" t="n">
-        <v>49800</v>
+        <v>16620</v>
       </c>
       <c r="Q6" t="n">
-        <v>8180</v>
+        <v>4600</v>
       </c>
       <c r="R6" t="n">
-        <v>114000</v>
+        <v>1000</v>
       </c>
       <c r="S6" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>루닛, 미국 FDA 승인 신청 및 AI 신약개발 기대감으로 인한 긍정적 전망. 전고점 돌파 가능성 언급.</t>
+          <t>건설 경기 전환점 및 주봉 차트 분석 기반 긍정적 전망. 지수 급락 속 상한가 기대감. 유상증자 이후 주가 흐름 주시.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FDA 승인', 'AI 신약개발', '헬스케어']</t>
+          <t>['건설경기', '차트분석', '유상증자']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9130</v>
+        <v>15790</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.41%</t>
+          <t>'+5.41%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="H7" t="n">
-        <v>2.67</v>
+        <v>7.15</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8580</v>
+        <v>14980</v>
       </c>
       <c r="K7" t="n">
-        <v>11090</v>
+        <v>14980</v>
       </c>
       <c r="L7" t="n">
-        <v>11150</v>
+        <v>16150</v>
       </c>
       <c r="M7" t="n">
-        <v>8400</v>
+        <v>14610</v>
       </c>
       <c r="N7" t="n">
-        <v>2.66</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>19000213305</v>
+        <v>33023827200</v>
       </c>
       <c r="P7" t="n">
-        <v>19270</v>
+        <v>49800</v>
       </c>
       <c r="Q7" t="n">
-        <v>2135</v>
+        <v>8180</v>
       </c>
       <c r="R7" t="n">
-        <v>-341000</v>
+        <v>114000</v>
       </c>
       <c r="S7" t="n">
-        <v>-2000</v>
+        <v>26000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>서울바이오시스, 광통신 사업 확대 및 신기술 기대감에도 불구하고 주가 부진 및 외국인 매도세 발생.</t>
+          <t>유방암 위험 예측 솔루션 '루닛 인사이트 리스크' 미 FDA 승인 신청. 2027년 AI 신약 개발 기대주로 주목. 전고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['광통신', '신기술', '매출']</t>
+          <t>['AI신약개발', 'FDA승인', '헬스케어']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6610</v>
+        <v>9040</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.93%</t>
+          <t>'+5.36%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6240</v>
+        <v>8580</v>
       </c>
       <c r="K8" t="n">
-        <v>6700</v>
+        <v>11090</v>
       </c>
       <c r="L8" t="n">
-        <v>7670</v>
+        <v>11150</v>
       </c>
       <c r="M8" t="n">
-        <v>6330</v>
+        <v>8400</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>11716053655</v>
+        <v>21092969720</v>
       </c>
       <c r="P8" t="n">
-        <v>16620</v>
+        <v>19270</v>
       </c>
       <c r="Q8" t="n">
-        <v>4600</v>
+        <v>2135</v>
       </c>
       <c r="R8" t="n">
-        <v>1000</v>
+        <v>-341000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>건설 경기 전환점 및 풍부한 재료를 기반으로 한 주봉 차트 분석. 유상증자 이후의 불확실성 언급.</t>
+          <t>서울반도체와의 연관성 및 기술 협력 언급. 광통신 사업 확장 기대. 신기술 대비 주가 부진에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['건설 경기', '주봉 차트', '유상증자']</t>
+          <t>['광통신', '신기술', '양산']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50000</v>
+        <v>49600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.83%</t>
+          <t>'+1.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F9" t="n">
         <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="H9" t="n">
         <v>23.82</v>
@@ -1254,7 +1254,7 @@
         <v>24.64</v>
       </c>
       <c r="O9" t="n">
-        <v>33792201225</v>
+        <v>35224620650</v>
       </c>
       <c r="P9" t="n">
         <v>97900</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표 기반 긍정 전망. TC본더 매출, 글로벌 수요 및 기술력 언급.</t>
+          <t>최대 실적 발표에도 불구하고 주가 하락세 지속. TC본더 매출 본격화 및 글로벌 수요 증가 등 긍정적 요인에도 불구하고 공매도 압력 존재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', '글로벌 수요']</t>
+          <t>['실적', 'TC본더', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15850</v>
+        <v>15760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.83%</t>
+          <t>'+0.25%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
         <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>207</v>
+        <v>182</v>
       </c>
       <c r="H10" t="n">
         <v>28.13</v>
@@ -1346,7 +1346,7 @@
         <v>28.07</v>
       </c>
       <c r="O10" t="n">
-        <v>22146264860</v>
+        <v>24129607900</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 조선주 폭등 대비 한국 조선주 기회론. 연기금, 기관 매수 언급 및 9배, 10배 상승 기대.</t>
+          <t>미국 조선주 폭등과 대비되는 국내 조선주 상황. 증권사 리포트와 기관 수급 유입 가능성 언급하며 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선주', '연기금', '기관']</t>
+          <t>['조선주', '리포트', '수급']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61200</v>
+        <v>60900</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.21</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="H11" t="n">
         <v>41.76</v>
@@ -1438,7 +1438,7 @@
         <v>41.55</v>
       </c>
       <c r="O11" t="n">
-        <v>39323744250</v>
+        <v>42074125100</v>
       </c>
       <c r="P11" t="n">
         <v>67300</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>반도체 하락 시 삼성E&amp;A 상승론. 자사주 취득, LOA 본 계약 체결 공시 기대.</t>
+          <t>자사주 취득 및 2월 LOA 본계약 체결 공시 기대감. 중동 대규모 수주 가능성 언급하며 주가 상승 전망. 외인 지분율 변화 주목.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주', 'LOA', '중동 수주']</t>
+          <t>['자사주', 'LOA', '수주']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54700</v>
+        <v>54300</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-4.23%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.2</v>
       </c>
       <c r="E12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="F12" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G12" t="n">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="H12" t="n">
         <v>22.14</v>
@@ -1530,7 +1530,7 @@
         <v>22.34</v>
       </c>
       <c r="O12" t="n">
-        <v>36127359450</v>
+        <v>39545201250</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>220750</v>
+        <v>11000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.85%</t>
+          <t>'-5.34%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>233</v>
       </c>
       <c r="F13" t="n">
-        <v>536</v>
+        <v>130</v>
       </c>
       <c r="G13" t="n">
-        <v>1279</v>
+        <v>792</v>
       </c>
       <c r="H13" t="n">
-        <v>46.17</v>
+        <v>9.73</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>232000</v>
+        <v>11620</v>
       </c>
       <c r="K13" t="n">
-        <v>223500</v>
+        <v>11300</v>
       </c>
       <c r="L13" t="n">
-        <v>229500</v>
+        <v>11470</v>
       </c>
       <c r="M13" t="n">
-        <v>220000</v>
+        <v>10960</v>
       </c>
       <c r="N13" t="n">
-        <v>46.19</v>
+        <v>9.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1138317858750</v>
+        <v>29873888265</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>1338000</v>
+        <v>101000</v>
       </c>
       <c r="S13" t="n">
-        <v>-249000</v>
+        <v>-32000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>이재용 증여세 및 상속세 관련 비판과 대국민 역적주 규탄. 외인 배당 매수 언급.</t>
+          <t>한수원 갑질 거절 및 원전 관련 호재 기대감. 공매도 금지 조치와 가덕도 신공항 흑자 전환 전망으로 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['증여세', '상속세', '배당']</t>
+          <t>['원전', '가덕도', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11040</v>
+        <v>219500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.99%</t>
+          <t>'-5.39%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>224</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>129</v>
+        <v>530</v>
       </c>
       <c r="G14" t="n">
-        <v>772</v>
+        <v>1269</v>
       </c>
       <c r="H14" t="n">
-        <v>9.73</v>
+        <v>46.17</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>11620</v>
+        <v>232000</v>
       </c>
       <c r="K14" t="n">
-        <v>11300</v>
+        <v>223500</v>
       </c>
       <c r="L14" t="n">
-        <v>11470</v>
+        <v>229500</v>
       </c>
       <c r="M14" t="n">
-        <v>10960</v>
+        <v>219000</v>
       </c>
       <c r="N14" t="n">
-        <v>9.6</v>
+        <v>46.19</v>
       </c>
       <c r="O14" t="n">
-        <v>27142207805</v>
+        <v>1248655655000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>94500</v>
       </c>
       <c r="R14" t="n">
-        <v>101000</v>
+        <v>1338000</v>
       </c>
       <c r="S14" t="n">
-        <v>-32000</v>
+        <v>-249000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>한수원 갑질 거절 및 원전 컨소시엄 불참 호재 분석. 가덕도 신공항 관련 언급.</t>
+          <t>이재용 회장의 경영 능력 및 도덕성에 대한 강한 비판과 함께 세무 조사 촉구. 증여세 절감 목적 의혹 제기로 주가 하락 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '가덕도']</t>
+          <t>['이재용', '주주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14140</v>
+        <v>13990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.92%</t>
+          <t>'-6.92%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="H15" t="n">
         <v>3.13</v>
@@ -1800,13 +1800,13 @@
         <v>14570</v>
       </c>
       <c r="M15" t="n">
-        <v>14010</v>
+        <v>13990</v>
       </c>
       <c r="N15" t="n">
         <v>3.33</v>
       </c>
       <c r="O15" t="n">
-        <v>22367583595</v>
+        <v>25173702265</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대한광통신, 광통신 섹터 전반의 변동성 및 해외 시장 하락세 영향. 단기 조정 가능성 언급.</t>
+          <t>광통신 섹터 전반의 변동성 우려. 정부 정책 지원 가능성 언급. 루멘텀 홀딩스, 마벨 등 관련주 동향 주시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '주가', '변동성']</t>
+          <t>['광통신', '정부정책', '변동성']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7380</v>
+        <v>7310</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.58%</t>
+          <t>'-7.47%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.03</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" t="n">
         <v>0.39</v>
@@ -1898,7 +1898,7 @@
         <v>0.42</v>
       </c>
       <c r="O16" t="n">
-        <v>12003990000</v>
+        <v>12353690985</v>
       </c>
       <c r="P16" t="n">
         <v>10300</v>
@@ -1958,13 +1958,13 @@
         <v>-0.63</v>
       </c>
       <c r="E17" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F17" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G17" t="n">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="H17" t="n">
         <v>11.6</v>
@@ -1990,7 +1990,7 @@
         <v>12.23</v>
       </c>
       <c r="O17" t="n">
-        <v>48960141425</v>
+        <v>52071890375</v>
       </c>
       <c r="P17" t="n">
         <v>59300</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>김동원 부회장 주가 누르기 의혹 제기. 태양광 및 RE100 관련 내용 포함.</t>
+          <t>한화 김동원 부회장의 주가 누르기 의혹 제기와 함께 급락세에 대한 불만 표출. 태양광 사업 실적 일부 호재에도 불구하고 주가 하락 지속.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['태양광', 'RE100', '주가조작']</t>
+          <t>['주가 누르기', '태양광', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1401000</v>
+        <v>1391000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.19%</t>
+          <t>'-8.85%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>800</v>
       </c>
       <c r="F18" t="n">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="G18" t="n">
-        <v>1222</v>
+        <v>1128</v>
       </c>
       <c r="H18" t="n">
         <v>48.72</v>
@@ -2076,13 +2076,13 @@
         <v>1446000</v>
       </c>
       <c r="M18" t="n">
-        <v>1401000</v>
+        <v>1389000</v>
       </c>
       <c r="N18" t="n">
         <v>48.66</v>
       </c>
       <c r="O18" t="n">
-        <v>1429907230500</v>
+        <v>1630045832500</v>
       </c>
       <c r="P18" t="n">
         <v>2987000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외인 기관 매도 및 계단식 하락 우려. 공산좌파, 빨갱이 등 정치적 비난 다수 포함.</t>
+          <t>주가 하락 지속에 대한 불만과 함께 정치적 요인(공산좌파, 재명이) 언급. 외인/기관 매도세 지속으로 계단식 하락 우려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외인', '기관', '계단식 하락']</t>
+          <t>['주가 하락', '외인 매도', '계단식 하락']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>120500</v>
+        <v>118400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-12.81%</t>
+          <t>'-14.33%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.26</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="H19" t="n">
         <v>14.2</v>
@@ -2168,13 +2168,13 @@
         <v>132900</v>
       </c>
       <c r="M19" t="n">
-        <v>119500</v>
+        <v>118000</v>
       </c>
       <c r="N19" t="n">
         <v>14.46</v>
       </c>
       <c r="O19" t="n">
-        <v>69099208800</v>
+        <v>76614399450</v>
       </c>
       <c r="P19" t="n">
         <v>198000</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK하이닉스 물량 확대 관련 언급. 실적 발표 전 급락 및 외인 지속 매도에 대한 우려.</t>
+          <t>SK하이닉스 물량 확대 등 긍정적 실적 전망에도 불구하고 주가 급락. 실적 발표 전 의도적인 주가 하락 의혹 및 외인 매도 지속.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적', '외인 매도', '공매도']</t>
+          <t>['실적', '주가 급락', '외인 매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13660</v>
+        <v>13610</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-19.65%</t>
+          <t>'-19.94%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F20" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H20" t="n">
         <v>0.66</v>
@@ -2266,7 +2266,7 @@
         <v>0.65</v>
       </c>
       <c r="O20" t="n">
-        <v>23773386100</v>
+        <v>24591840500</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>멜콘, 보호예수 물량 해소 후 반도체 섹터 성장 기대감 있으나, 단기 변동성 및 가격 논란 존재.</t>
+          <t>보호예수 물량 해소 후 품절주 가능성 언급. 반도체 생산량 3배 증가. 제2의 한미반도체, HBM, 데이터센터 관련 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '반도체', '공모주']</t>
+          <t>['HBM', '반도체', '품절주']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,79 +2311,79 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>벡트로보틱스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10700</v>
+        <v>1869</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-28.67%</t>
+          <t>'-27.42%</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E21" t="n">
+        <v>46</v>
+      </c>
+      <c r="F21" t="n">
+        <v>27</v>
+      </c>
+      <c r="G21" t="n">
+        <v>23</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2575</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1811</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O21" t="n">
+        <v>5786659741</v>
+      </c>
+      <c r="P21" t="n">
+        <v>5700</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R21" t="n">
+        <v>219000</v>
+      </c>
+      <c r="S21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="n">
-        <v>185</v>
-      </c>
-      <c r="F21" t="n">
-        <v>97</v>
-      </c>
-      <c r="G21" t="n">
-        <v>169</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M21" t="n">
-        <v>9790</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>74090588300</v>
-      </c>
-      <c r="P21" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>9790</v>
-      </c>
-      <c r="R21" t="n">
-        <v>-40000</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-168000</v>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>크리에이츠, 높은 당기순이익에도 불구하고 공모주 시세 및 환매 청구 관련 부정적 전망.</t>
+          <t>주가 폭락 지속, 하한가 우려. 실적 부진 언급. 외국인 대량 순매수 이유 불명확.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['당기순이익', '공모주', '환매청구']</t>
+          <t>['폭락', '실적', '외국인']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2395,6 +2395,98 @@
         </is>
       </c>
       <c r="Z21" t="inlineStr">
+        <is>
+          <t>457600</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10250</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-31.67%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>201</v>
+      </c>
+      <c r="F22" t="n">
+        <v>106</v>
+      </c>
+      <c r="G22" t="n">
+        <v>227</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M22" t="n">
+        <v>9790</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>80341204125</v>
+      </c>
+      <c r="P22" t="n">
+        <v>12700</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9790</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-168000</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>실내골프대회 개최 및 대중화 기대감 반영. 당기순이익 216억, 현금 900억 보유. 공모주 상장 후 손바뀜 거래량 상당.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['대중화', '당기순이익', '공모주']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>439270</t>
         </is>

--- a/data/trending_integrated_20261030_10.xlsx
+++ b/data/trending_integrated_20261030_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18220</v>
+        <v>17500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+102.44%</t>
+          <t>'+94.44%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="F2" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -604,19 +604,19 @@
         <v>21700</v>
       </c>
       <c r="M2" t="n">
-        <v>17920</v>
+        <v>17140</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>207787144850</v>
+        <v>222708579170</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
       </c>
       <c r="Q2" t="n">
-        <v>17920</v>
+        <v>17140</v>
       </c>
       <c r="R2" t="n">
         <v>-161000</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주의 높은 변동성과 단기 급등락 반복. 크리에이츠와의 이익 비교 및 유통 물량 적은 점을 들어 장기 보유 시 상승 기대.</t>
+          <t>신규 상장주에 대한 부정적 평가 및 단타 매매 집중. 주가 하락 및 매도세 지속. 낮은 거래량 및 불확실성 강조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규상장주', '변동성', '유통물량']</t>
+          <t>['신규 상장주', '단타', '주가 하락']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,79 +655,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8860</v>
+        <v>12860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.06%</t>
+          <t>'+14.82%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.37</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>216</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>618</v>
       </c>
       <c r="H3" t="n">
-        <v>13.29</v>
+        <v>15.04</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7700</v>
+        <v>11200</v>
       </c>
       <c r="K3" t="n">
-        <v>9360</v>
+        <v>13500</v>
       </c>
       <c r="L3" t="n">
-        <v>9500</v>
+        <v>13710</v>
       </c>
       <c r="M3" t="n">
-        <v>8610</v>
+        <v>12100</v>
       </c>
       <c r="N3" t="n">
-        <v>12.92</v>
+        <v>15.08</v>
       </c>
       <c r="O3" t="n">
-        <v>5513696590</v>
+        <v>32321659530</v>
       </c>
       <c r="P3" t="n">
-        <v>13670</v>
+        <v>18960</v>
       </c>
       <c r="Q3" t="n">
-        <v>7060</v>
+        <v>5730</v>
       </c>
       <c r="R3" t="n">
-        <v>-73000</v>
+        <v>-260000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3상 성공 가능성에도 불구하고 역류성 식도염 시장 규모 제한 및 경쟁 심화 우려. 외인/기관 매도세로 주가 하락 예상.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 성공. 100억 달러 시장 석권 기대감. 2연상 기록, 공매도 세력 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['3상 성공', '시장 규모', '경쟁']</t>
+          <t>['백색LED', '희토류', '기술개발']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12760</v>
+        <v>8820</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.93%</t>
+          <t>'+14.55%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>0.37</v>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>599</v>
+        <v>74</v>
       </c>
       <c r="H4" t="n">
-        <v>15.04</v>
+        <v>13.29</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11200</v>
+        <v>7700</v>
       </c>
       <c r="K4" t="n">
-        <v>13500</v>
+        <v>9360</v>
       </c>
       <c r="L4" t="n">
-        <v>13710</v>
+        <v>9500</v>
       </c>
       <c r="M4" t="n">
-        <v>12100</v>
+        <v>8610</v>
       </c>
       <c r="N4" t="n">
-        <v>15.08</v>
+        <v>12.92</v>
       </c>
       <c r="O4" t="n">
-        <v>31020676580</v>
+        <v>5625970340</v>
       </c>
       <c r="P4" t="n">
-        <v>18960</v>
+        <v>13670</v>
       </c>
       <c r="Q4" t="n">
-        <v>5730</v>
+        <v>7060</v>
       </c>
       <c r="R4" t="n">
-        <v>-260000</v>
+        <v>-73000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 성공. 100억 달러 시장 석권 기대감. 2연상 기록, 공매도 세력 언급.</t>
+          <t>3상 성공 가능성에도 불구하고 역류성 식도염 시장 규모 제한 및 경쟁 심화 우려. 외인/기관 매도세로 주가 하락 예상.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['백색LED', '희토류', '기술개발']</t>
+          <t>['3상 성공', '시장 규모', '경쟁']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18510</v>
+        <v>18670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.17%</t>
+          <t>'+12.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.75</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="H5" t="n">
         <v>3.6</v>
@@ -886,7 +886,7 @@
         <v>4.35</v>
       </c>
       <c r="O5" t="n">
-        <v>55081952545</v>
+        <v>56519861190</v>
       </c>
       <c r="P5" t="n">
         <v>22450</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>11월 양자 관련법 시행 시 최대 수혜 기대. 보안주로서의 성장 가능성 언급. 거래량 대비 주가 하락에 대한 의문 제기.</t>
+          <t>보안 대장주로서의 기대감 및 11월 양자관련법 시행 최대 수혜 전망. 해킹 이슈와 타 보안주 흐름 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '기술력']</t>
+          <t>['보안주', '양자보안', '최대수혜']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6870</v>
+        <v>6850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.10%</t>
+          <t>'+9.78%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>12222277855</v>
+        <v>12701665890</v>
       </c>
       <c r="P6" t="n">
         <v>16620</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>건설 경기 전환점 및 주봉 차트 분석 기반 긍정적 전망. 지수 급락 속 상한가 기대감. 유상증자 이후 주가 흐름 주시.</t>
+          <t>연속 상승 후 하락세 전환 및 유상증자 이후 전망 부정적. 재탕 삼탕 뉴스에 대한 의구심 표현.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설경기', '차트분석', '유상증자']</t>
+          <t>['유상증자', '하락세', '건설']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15790</v>
+        <v>7220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.41%</t>
+          <t>'+8.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.9</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F7" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>7.15</v>
+        <v>0.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14980</v>
+        <v>6640</v>
       </c>
       <c r="K7" t="n">
-        <v>14980</v>
+        <v>7210</v>
       </c>
       <c r="L7" t="n">
-        <v>16150</v>
+        <v>7500</v>
       </c>
       <c r="M7" t="n">
-        <v>14610</v>
+        <v>6730</v>
       </c>
       <c r="N7" t="n">
-        <v>8.050000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="O7" t="n">
-        <v>33023827200</v>
+        <v>25383994415</v>
       </c>
       <c r="P7" t="n">
-        <v>49800</v>
+        <v>9820</v>
       </c>
       <c r="Q7" t="n">
-        <v>8180</v>
+        <v>4000</v>
       </c>
       <c r="R7" t="n">
-        <v>114000</v>
+        <v>-46000</v>
       </c>
       <c r="S7" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 '루닛 인사이트 리스크' 미 FDA 승인 신청. 2027년 AI 신약 개발 기대주로 주목. 전고점 돌파 기대.</t>
+          <t>594억 규모 공급 계약 체결 사실과 함께 주포의 움직임, 유통 물량 관련 언급. BPS 13300원 기준으로의 하단 지지력 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['AI신약개발', 'FDA승인', '헬스케어']</t>
+          <t>['공급계약', 'BPS', '주포']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9040</v>
+        <v>9200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.36%</t>
+          <t>'+7.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H8" t="n">
         <v>2.67</v>
@@ -1162,7 +1162,7 @@
         <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>21092969720</v>
+        <v>21738558540</v>
       </c>
       <c r="P8" t="n">
         <v>19270</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>서울반도체와의 연관성 및 기술 협력 언급. 광통신 사업 확장 기대. 신기술 대비 주가 부진에 대한 아쉬움 표출.</t>
+          <t>내년 조단위 매출 및 광통신 사업 가세 가능성 언급. 와이캅 칩 설계/생산 관련 내용과 인텔 어닝쇼크 영향 분석.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '신기술', '양산']</t>
+          <t>['광통신', '칩설계', '매출']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49600</v>
+        <v>15860</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.02%</t>
+          <t>'+5.87%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.82</v>
+        <v>-0.9</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>129</v>
+        <v>216</v>
       </c>
       <c r="H9" t="n">
-        <v>23.82</v>
+        <v>7.15</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>49100</v>
+        <v>14980</v>
       </c>
       <c r="K9" t="n">
-        <v>49450</v>
+        <v>14980</v>
       </c>
       <c r="L9" t="n">
-        <v>52000</v>
+        <v>16150</v>
       </c>
       <c r="M9" t="n">
-        <v>48050</v>
+        <v>14610</v>
       </c>
       <c r="N9" t="n">
-        <v>24.64</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>35224620650</v>
+        <v>35234397975</v>
       </c>
       <c r="P9" t="n">
-        <v>97900</v>
+        <v>49800</v>
       </c>
       <c r="Q9" t="n">
-        <v>30950</v>
+        <v>8180</v>
       </c>
       <c r="R9" t="n">
-        <v>-85000</v>
+        <v>114000</v>
       </c>
       <c r="S9" t="n">
-        <v>36000</v>
+        <v>26000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>최대 실적 발표에도 불구하고 주가 하락세 지속. TC본더 매출 본격화 및 글로벌 수요 증가 등 긍정적 요인에도 불구하고 공매도 압력 존재.</t>
+          <t>유방암 위험 예측 솔루션 '루닛 인사이트 리스크' 미 FDA 승인 신청 및 췌장암 검사 FDA 허가 신청 관련 호재. AI 신약개발 기대주로 NH투자증권 주목.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', '공매도']</t>
+          <t>['FDA승인', 'AI신약', '헬스케어']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15760</v>
+        <v>29300</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.25%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="H10" t="n">
-        <v>28.13</v>
+        <v>4.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>15720</v>
+        <v>28050</v>
       </c>
       <c r="K10" t="n">
-        <v>15420</v>
+        <v>27850</v>
       </c>
       <c r="L10" t="n">
-        <v>16050</v>
+        <v>30400</v>
       </c>
       <c r="M10" t="n">
-        <v>15320</v>
+        <v>27650</v>
       </c>
       <c r="N10" t="n">
-        <v>28.07</v>
+        <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>24129607900</v>
+        <v>89068246650</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>50600</v>
       </c>
       <c r="Q10" t="n">
-        <v>15320</v>
+        <v>13210</v>
       </c>
       <c r="R10" t="n">
-        <v>231000</v>
+        <v>-64000</v>
       </c>
       <c r="S10" t="n">
-        <v>14000</v>
+        <v>41000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 조선주 폭등과 대비되는 국내 조선주 상황. 증권사 리포트와 기관 수급 유입 가능성 언급하며 상승 기대감 형성.</t>
+          <t>로봇손 관련 신규 사업 진출 및 정밀 엑추에이터 시장 진입 소식에 따른 상승 기대. 계단식 상승 및 기관 매수세 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선주', '리포트', '수급']</t>
+          <t>['로봇손', '엑추에이터', '기관매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60900</v>
+        <v>49850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'+1.53%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.21</v>
+        <v>-0.82</v>
       </c>
       <c r="E11" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="H11" t="n">
-        <v>41.76</v>
+        <v>23.82</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>62800</v>
+        <v>49100</v>
       </c>
       <c r="K11" t="n">
-        <v>62300</v>
+        <v>49450</v>
       </c>
       <c r="L11" t="n">
-        <v>62800</v>
+        <v>52000</v>
       </c>
       <c r="M11" t="n">
-        <v>60800</v>
+        <v>48050</v>
       </c>
       <c r="N11" t="n">
-        <v>41.55</v>
+        <v>24.64</v>
       </c>
       <c r="O11" t="n">
-        <v>42074125100</v>
+        <v>36279312025</v>
       </c>
       <c r="P11" t="n">
-        <v>67300</v>
+        <v>97900</v>
       </c>
       <c r="Q11" t="n">
-        <v>23150</v>
+        <v>30950</v>
       </c>
       <c r="R11" t="n">
-        <v>69000</v>
+        <v>-85000</v>
       </c>
       <c r="S11" t="n">
-        <v>-10000</v>
+        <v>36000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>자사주 취득 및 2월 LOA 본계약 체결 공시 기대감. 중동 대규모 수주 가능성 언급하며 주가 상승 전망. 외인 지분율 변화 주목.</t>
+          <t>최대 실적 발표에도 불구하고 주가 상승 미미. TC본더 매출 본격화 및 공매도 쇼트 스퀴즈 기대. 저평가된 PER 및 글로벌 수요 증가 긍정적 요인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['자사주', 'LOA', '수주']</t>
+          <t>['실적', 'TC본더', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54300</v>
+        <v>15830</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.23%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>177</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>655</v>
+        <v>187</v>
       </c>
       <c r="H12" t="n">
-        <v>22.14</v>
+        <v>28.13</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>56700</v>
+        <v>15720</v>
       </c>
       <c r="K12" t="n">
-        <v>55500</v>
+        <v>15420</v>
       </c>
       <c r="L12" t="n">
-        <v>55900</v>
+        <v>16050</v>
       </c>
       <c r="M12" t="n">
-        <v>54000</v>
+        <v>15320</v>
       </c>
       <c r="N12" t="n">
-        <v>22.34</v>
+        <v>28.07</v>
       </c>
       <c r="O12" t="n">
-        <v>39545201250</v>
+        <v>26344332380</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>53400</v>
+        <v>15320</v>
       </c>
       <c r="R12" t="n">
-        <v>-85000</v>
+        <v>231000</v>
       </c>
       <c r="S12" t="n">
-        <v>-58000</v>
+        <v>14000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선. 다만, 체코 원전 사업 실패 경험과 정치적 불확실성으로 인한 변동성.</t>
+          <t>미국 조선주 폭등 대비 국내 조선주 기회 언급. 야간 선물 하락 및 신용 물량 출회 우려. 증권사 리포트 및 기대감 반영. 단기 투자자 경계.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['SMR', '뉴스케일파워', '원전']</t>
+          <t>['조선주', '기회', '증권사 리포트']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11000</v>
+        <v>60900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.34%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>233</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>792</v>
+        <v>199</v>
       </c>
       <c r="H13" t="n">
-        <v>9.73</v>
+        <v>41.76</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>11620</v>
+        <v>62800</v>
       </c>
       <c r="K13" t="n">
-        <v>11300</v>
+        <v>62300</v>
       </c>
       <c r="L13" t="n">
-        <v>11470</v>
+        <v>62800</v>
       </c>
       <c r="M13" t="n">
-        <v>10960</v>
+        <v>60700</v>
       </c>
       <c r="N13" t="n">
-        <v>9.6</v>
+        <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>29873888265</v>
+        <v>46081455900</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R13" t="n">
-        <v>101000</v>
+        <v>69000</v>
       </c>
       <c r="S13" t="n">
-        <v>-32000</v>
+        <v>-10000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>한수원 갑질 거절 및 원전 관련 호재 기대감. 공매도 금지 조치와 가덕도 신공항 흑자 전환 전망으로 주가 상승 기대.</t>
+          <t>반도체 업황 부진 속 삼성E&amp;A 상승 기대. 자사주 취득 및 LOA 본계약 체결 공시 이슈. 중동 대규모 수주 공시 시 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '가덕도', '공매도']</t>
+          <t>['자사주 취득', 'LOA', '대규모 수주']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>219500</v>
+        <v>54500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.39%</t>
+          <t>'-3.88%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>192</v>
       </c>
       <c r="F14" t="n">
-        <v>530</v>
+        <v>134</v>
       </c>
       <c r="G14" t="n">
-        <v>1269</v>
+        <v>672</v>
       </c>
       <c r="H14" t="n">
-        <v>46.17</v>
+        <v>22.14</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>232000</v>
+        <v>56700</v>
       </c>
       <c r="K14" t="n">
-        <v>223500</v>
+        <v>55500</v>
       </c>
       <c r="L14" t="n">
-        <v>229500</v>
+        <v>55900</v>
       </c>
       <c r="M14" t="n">
-        <v>219000</v>
+        <v>54000</v>
       </c>
       <c r="N14" t="n">
-        <v>46.19</v>
+        <v>22.34</v>
       </c>
       <c r="O14" t="n">
-        <v>1248655655000</v>
+        <v>42644780800</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>94500</v>
+        <v>53400</v>
       </c>
       <c r="R14" t="n">
-        <v>1338000</v>
+        <v>-85000</v>
       </c>
       <c r="S14" t="n">
-        <v>-249000</v>
+        <v>-58000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이재용 회장의 경영 능력 및 도덕성에 대한 강한 비판과 함께 세무 조사 촉구. 증여세 절감 목적 의혹 제기로 주가 하락 기대.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 전망. 체코 원전 사업 관련 비판과 함께 원전주 상승 가능성 언급. 실적과 무관한 주가 움직임에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['이재용', '주주']</t>
+          <t>['SMR', '수주', '실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13990</v>
+        <v>11030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.92%</t>
+          <t>'-5.08%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.2</v>
+        <v>0.13</v>
       </c>
       <c r="E15" t="n">
-        <v>66</v>
+        <v>249</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>132</v>
       </c>
       <c r="G15" t="n">
-        <v>233</v>
+        <v>823</v>
       </c>
       <c r="H15" t="n">
-        <v>3.13</v>
+        <v>9.73</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15030</v>
+        <v>11620</v>
       </c>
       <c r="K15" t="n">
-        <v>14500</v>
+        <v>11300</v>
       </c>
       <c r="L15" t="n">
-        <v>14570</v>
+        <v>11470</v>
       </c>
       <c r="M15" t="n">
-        <v>13990</v>
+        <v>10960</v>
       </c>
       <c r="N15" t="n">
-        <v>3.33</v>
+        <v>9.6</v>
       </c>
       <c r="O15" t="n">
-        <v>25173702265</v>
+        <v>32192405765</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>1830</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>8000</v>
+        <v>101000</v>
       </c>
       <c r="S15" t="n">
-        <v>-9000</v>
+        <v>-32000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>광통신 섹터 전반의 변동성 우려. 정부 정책 지원 가능성 언급. 루멘텀 홀딩스, 마벨 등 관련주 동향 주시.</t>
+          <t>한수원 갑질 거절 및 원전 관련 호재 기대감. 공매도 금지 조치와 가덕도 신공항 흑자 전환 전망으로 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '정부정책', '변동성']</t>
+          <t>['원전', '가덕도', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7310</v>
+        <v>219250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.47%</t>
+          <t>'-5.50%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>508</v>
       </c>
       <c r="G16" t="n">
-        <v>87</v>
+        <v>1242</v>
       </c>
       <c r="H16" t="n">
-        <v>0.39</v>
+        <v>46.17</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>7900</v>
+        <v>232000</v>
       </c>
       <c r="K16" t="n">
-        <v>7790</v>
+        <v>223500</v>
       </c>
       <c r="L16" t="n">
-        <v>8130</v>
+        <v>229500</v>
       </c>
       <c r="M16" t="n">
-        <v>7150</v>
+        <v>219000</v>
       </c>
       <c r="N16" t="n">
-        <v>0.42</v>
+        <v>46.19</v>
       </c>
       <c r="O16" t="n">
-        <v>12353690985</v>
+        <v>1331571653750</v>
       </c>
       <c r="P16" t="n">
-        <v>10300</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>952</v>
+        <v>94500</v>
       </c>
       <c r="R16" t="n">
-        <v>-11000</v>
+        <v>1338000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-249000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
+          <t>노조의 주가 하락 기도 및 이재용 회장의 증여세 관련 비판. 주가 하락 시 이익을 보는 회장 체제에 대한 의문 제기. 미국 상장 시 비교 및 국내 증시 상황 비판.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['공급계약', '재료', '주가']</t>
+          <t>['노조', '증여세', '주가 하락']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21750</v>
+        <v>13960</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.84%</t>
+          <t>'-7.12%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.63</v>
+        <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="F17" t="n">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>369</v>
+        <v>241</v>
       </c>
       <c r="H17" t="n">
-        <v>11.6</v>
+        <v>3.13</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>23600</v>
+        <v>15030</v>
       </c>
       <c r="K17" t="n">
-        <v>22650</v>
+        <v>14500</v>
       </c>
       <c r="L17" t="n">
-        <v>22700</v>
+        <v>14570</v>
       </c>
       <c r="M17" t="n">
-        <v>21100</v>
+        <v>13920</v>
       </c>
       <c r="N17" t="n">
-        <v>12.23</v>
+        <v>3.33</v>
       </c>
       <c r="O17" t="n">
-        <v>52071890375</v>
+        <v>27098000990</v>
       </c>
       <c r="P17" t="n">
-        <v>59300</v>
+        <v>31500</v>
       </c>
       <c r="Q17" t="n">
-        <v>21100</v>
+        <v>1830</v>
       </c>
       <c r="R17" t="n">
-        <v>-481000</v>
+        <v>8000</v>
       </c>
       <c r="S17" t="n">
-        <v>-144000</v>
+        <v>-9000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>한화 김동원 부회장의 주가 누르기 의혹 제기와 함께 급락세에 대한 불만 표출. 태양광 사업 실적 일부 호재에도 불구하고 주가 하락 지속.</t>
+          <t>미국 광통신주 급락 및 마벨 14% 폭락 영향으로 인한 조정 예상. 정부 및 청와대 정책 기대감 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 누르기', '태양광', '실적']</t>
+          <t>['광통신', '조정', '정책']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1391000</v>
+        <v>21850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.85%</t>
+          <t>'-7.42%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06</v>
+        <v>-0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>800</v>
+        <v>152</v>
       </c>
       <c r="F18" t="n">
-        <v>522</v>
+        <v>121</v>
       </c>
       <c r="G18" t="n">
-        <v>1128</v>
+        <v>388</v>
       </c>
       <c r="H18" t="n">
-        <v>48.72</v>
+        <v>11.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1526000</v>
+        <v>23600</v>
       </c>
       <c r="K18" t="n">
-        <v>1444000</v>
+        <v>22650</v>
       </c>
       <c r="L18" t="n">
-        <v>1446000</v>
+        <v>22700</v>
       </c>
       <c r="M18" t="n">
-        <v>1389000</v>
+        <v>21100</v>
       </c>
       <c r="N18" t="n">
-        <v>48.66</v>
+        <v>12.23</v>
       </c>
       <c r="O18" t="n">
-        <v>1630045832500</v>
+        <v>54523720375</v>
       </c>
       <c r="P18" t="n">
-        <v>2987000</v>
+        <v>59300</v>
       </c>
       <c r="Q18" t="n">
-        <v>501000</v>
+        <v>21100</v>
       </c>
       <c r="R18" t="n">
-        <v>-65000</v>
+        <v>-481000</v>
       </c>
       <c r="S18" t="n">
-        <v>-80000</v>
+        <v>-144000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>주가 하락 지속에 대한 불만과 함께 정치적 요인(공산좌파, 재명이) 언급. 외인/기관 매도세 지속으로 계단식 하락 우려.</t>
+          <t>김동원 부회장의 주가 누르기 의혹 및 구속 수사 임박 가능성 제기. 태양광 수혜 및 RE100 승인 관련 내용 포함. 주가 하락폭에 대한 강한 불만 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 하락', '외인 매도', '계단식 하락']</t>
+          <t>['김동원 부회장', '주가 누르기', '태양광']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>118400</v>
+        <v>7290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-14.33%</t>
+          <t>'-7.72%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="H19" t="n">
-        <v>14.2</v>
+        <v>0.39</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>138200</v>
+        <v>7900</v>
       </c>
       <c r="K19" t="n">
-        <v>132600</v>
+        <v>7790</v>
       </c>
       <c r="L19" t="n">
-        <v>132900</v>
+        <v>8130</v>
       </c>
       <c r="M19" t="n">
-        <v>118000</v>
+        <v>7150</v>
       </c>
       <c r="N19" t="n">
-        <v>14.46</v>
+        <v>0.42</v>
       </c>
       <c r="O19" t="n">
-        <v>76614399450</v>
+        <v>12686255615</v>
       </c>
       <c r="P19" t="n">
-        <v>198000</v>
+        <v>10300</v>
       </c>
       <c r="Q19" t="n">
-        <v>36450</v>
+        <v>952</v>
       </c>
       <c r="R19" t="n">
-        <v>-162000</v>
+        <v>-11000</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK하이닉스 물량 확대 등 긍정적 실적 전망에도 불구하고 주가 급락. 실적 발표 전 의도적인 주가 하락 의혹 및 외인 매도 지속.</t>
+          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['실적', '주가 급락', '외인 매도']</t>
+          <t>['공급계약', '재료', '주가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13610</v>
+        <v>1389000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-19.94%</t>
+          <t>'-8.98%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="E20" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>523</v>
       </c>
       <c r="G20" t="n">
-        <v>87</v>
+        <v>1082</v>
       </c>
       <c r="H20" t="n">
-        <v>0.66</v>
+        <v>48.72</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>17000</v>
+        <v>1526000</v>
       </c>
       <c r="K20" t="n">
-        <v>14000</v>
+        <v>1444000</v>
       </c>
       <c r="L20" t="n">
-        <v>14900</v>
+        <v>1446000</v>
       </c>
       <c r="M20" t="n">
-        <v>13260</v>
+        <v>1387000</v>
       </c>
       <c r="N20" t="n">
-        <v>0.65</v>
+        <v>48.66</v>
       </c>
       <c r="O20" t="n">
-        <v>24591840500</v>
+        <v>1742693169000</v>
       </c>
       <c r="P20" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q20" t="n">
-        <v>11550</v>
+        <v>501000</v>
       </c>
       <c r="R20" t="n">
-        <v>-7000</v>
+        <v>-65000</v>
       </c>
       <c r="S20" t="n">
-        <v>-150000</v>
+        <v>-80000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 해소 후 품절주 가능성 언급. 반도체 생산량 3배 증가. 제2의 한미반도체, HBM, 데이터센터 관련 기대.</t>
+          <t>정치적 이슈와 연관된 주가 하락 원인 분석 및 비판. 외인 기관의 매도세 지속 및 단기 투자 대응 강조. 계단식 하락 및 개미 투자자 피해 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['HBM', '반도체', '품절주']</t>
+          <t>['정치적 이슈', '외인 기관', '계단식 하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,86 +2304,86 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>벡트로보틱스</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1869</v>
+        <v>118400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-27.42%</t>
+          <t>'-14.33%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.45</v>
+        <v>-0.26</v>
       </c>
       <c r="E21" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>14.2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2575</v>
+        <v>138200</v>
       </c>
       <c r="K21" t="n">
-        <v>1960</v>
+        <v>132600</v>
       </c>
       <c r="L21" t="n">
-        <v>2005</v>
+        <v>132900</v>
       </c>
       <c r="M21" t="n">
-        <v>1811</v>
+        <v>118000</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>14.46</v>
       </c>
       <c r="O21" t="n">
-        <v>5786659741</v>
+        <v>84004106900</v>
       </c>
       <c r="P21" t="n">
-        <v>5700</v>
+        <v>198000</v>
       </c>
       <c r="Q21" t="n">
-        <v>1401</v>
+        <v>36450</v>
       </c>
       <c r="R21" t="n">
-        <v>219000</v>
+        <v>-162000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 폭락 지속, 하한가 우려. 실적 부진 언급. 외국인 대량 순매수 이유 불명확.</t>
+          <t>실적 발표 전 급격한 주가 하락에 대한 의문 제기. SK하이닉스 소부장 물량 확대 언급. 수급 불안 및 외인 매도 지속. 실적 사전 인지 가능성 시사.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['폭락', '실적', '외국인']</t>
+          <t>['실적', '주가 하락', '외인 매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,38 +2396,38 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>457600</t>
+          <t>353200</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10250</v>
+        <v>13590</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-31.67%</t>
+          <t>'-20.06%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>201</v>
+        <v>120</v>
       </c>
       <c r="F22" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
-        <v>227</v>
+        <v>95</v>
       </c>
       <c r="H22" t="n">
-        <v>3.05</v>
+        <v>0.66</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="K22" t="n">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="L22" t="n">
-        <v>12700</v>
+        <v>14900</v>
       </c>
       <c r="M22" t="n">
-        <v>9790</v>
+        <v>13260</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="O22" t="n">
-        <v>80341204125</v>
+        <v>25173086740</v>
       </c>
       <c r="P22" t="n">
-        <v>12700</v>
+        <v>28800</v>
       </c>
       <c r="Q22" t="n">
-        <v>9790</v>
+        <v>11550</v>
       </c>
       <c r="R22" t="n">
-        <v>-40000</v>
+        <v>-7000</v>
       </c>
       <c r="S22" t="n">
-        <v>-168000</v>
+        <v>-150000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>실내골프대회 개최 및 대중화 기대감 반영. 당기순이익 216억, 현금 900억 보유. 공모주 상장 후 손바뀜 거래량 상당.</t>
+          <t>마이크론 퀠테스트 통과 및 반도체 생산량 3배 증가 소식 기반으로 보호예수 물량 해제 후 상승 기대. 초품절주 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,18 +2475,202 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['대중화', '당기순이익', '공모주']</t>
+          <t>['퀠테스트', '보호예수', '반도체']</t>
         </is>
       </c>
       <c r="X22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>벡트로보틱스</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1845</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-28.35%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E23" t="n">
+        <v>46</v>
+      </c>
+      <c r="F23" t="n">
+        <v>27</v>
+      </c>
+      <c r="G23" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>2575</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1811</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O23" t="n">
+        <v>5857928098</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5700</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R23" t="n">
+        <v>219000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>주가 폭락 지속, 하한가 우려. 실적 부진 언급. 외국인 대량 순매수 이유 불명확.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['폭락', '실적', '외국인']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
         <v>1</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>457600</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>10360</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>'-30.93%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>226</v>
+      </c>
+      <c r="F24" t="n">
+        <v>116</v>
+      </c>
+      <c r="G24" t="n">
+        <v>272</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M24" t="n">
+        <v>9790</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>83295262155</v>
+      </c>
+      <c r="P24" t="n">
+        <v>12700</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>9790</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-168000</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>실내 골프 사업 성장 가능성 언급. 상장 후 손바뀜 및 거래량 증가. 인텔리빅스와 비교 시 높은 순이익 및 현금 보유량 강조. 초기 상승 후 하락 마감.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>['실내 골프', '손바뀜', '순이익']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>439270</t>
         </is>

--- a/data/trending_integrated_20261030_10.xlsx
+++ b/data/trending_integrated_20261030_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17500</v>
+        <v>16670</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+94.44%</t>
+          <t>'+85.22%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="F2" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G2" t="n">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -604,19 +604,19 @@
         <v>21700</v>
       </c>
       <c r="M2" t="n">
-        <v>17140</v>
+        <v>16510</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>222708579170</v>
+        <v>234153725275</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
       </c>
       <c r="Q2" t="n">
-        <v>17140</v>
+        <v>16510</v>
       </c>
       <c r="R2" t="n">
         <v>-161000</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주에 대한 부정적 평가 및 단타 매매 집중. 주가 하락 및 매도세 지속. 낮은 거래량 및 불확실성 강조.</t>
+          <t>신규 상장주의 높은 변동성에 대한 우려. 단기 급등 후 급락하는 흐름에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장주', '단타', '주가 하락']</t>
+          <t>['신규 상장주', '변동성', '급락']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12860</v>
+        <v>19680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.82%</t>
+          <t>'+18.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.04</v>
+        <v>-0.75</v>
       </c>
       <c r="E3" t="n">
-        <v>216</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>44</v>
       </c>
       <c r="G3" t="n">
-        <v>618</v>
+        <v>97</v>
       </c>
       <c r="H3" t="n">
-        <v>15.04</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11200</v>
+        <v>16650</v>
       </c>
       <c r="K3" t="n">
-        <v>13500</v>
+        <v>16830</v>
       </c>
       <c r="L3" t="n">
-        <v>13710</v>
+        <v>19690</v>
       </c>
       <c r="M3" t="n">
-        <v>12100</v>
+        <v>16750</v>
       </c>
       <c r="N3" t="n">
-        <v>15.08</v>
+        <v>4.35</v>
       </c>
       <c r="O3" t="n">
-        <v>32321659530</v>
+        <v>65534977505</v>
       </c>
       <c r="P3" t="n">
-        <v>18960</v>
+        <v>22450</v>
       </c>
       <c r="Q3" t="n">
-        <v>5730</v>
+        <v>6320</v>
       </c>
       <c r="R3" t="n">
-        <v>-260000</v>
+        <v>59000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 성공. 100억 달러 시장 석권 기대감. 2연상 기록, 공매도 세력 언급.</t>
+          <t>양자암호화폐 관련 법 시행에 따른 수혜 기대감. 보안 대장주로서의 입지 강화 및 기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['백색LED', '희토류', '기술개발']</t>
+          <t>['양자암호', '보안', '기관']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8820</v>
+        <v>12930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.55%</t>
+          <t>'+15.45%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.37</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>223</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>143</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>617</v>
       </c>
       <c r="H4" t="n">
-        <v>13.29</v>
+        <v>15.04</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>7700</v>
+        <v>11200</v>
       </c>
       <c r="K4" t="n">
-        <v>9360</v>
+        <v>13500</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>13710</v>
       </c>
       <c r="M4" t="n">
-        <v>8610</v>
+        <v>12100</v>
       </c>
       <c r="N4" t="n">
-        <v>12.92</v>
+        <v>15.08</v>
       </c>
       <c r="O4" t="n">
-        <v>5625970340</v>
+        <v>34123304890</v>
       </c>
       <c r="P4" t="n">
-        <v>13670</v>
+        <v>18960</v>
       </c>
       <c r="Q4" t="n">
-        <v>7060</v>
+        <v>5730</v>
       </c>
       <c r="R4" t="n">
-        <v>-73000</v>
+        <v>-260000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3상 성공 가능성에도 불구하고 역류성 식도염 시장 규모 제한 및 경쟁 심화 우려. 외인/기관 매도세로 주가 하락 예상.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 시장 석권 가능성 언급. 강력한 기술력 기반의 긍정적 주가 전망 및 공매도 세력에 대한 경고.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['3상 성공', '시장 규모', '경쟁']</t>
+          <t>['백색LED', '희토류', '게임체인져']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18670</v>
+        <v>8740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.13%</t>
+          <t>'+13.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.75</v>
+        <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>13.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>16650</v>
+        <v>7700</v>
       </c>
       <c r="K5" t="n">
-        <v>16830</v>
+        <v>9360</v>
       </c>
       <c r="L5" t="n">
-        <v>19550</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>16750</v>
+        <v>8610</v>
       </c>
       <c r="N5" t="n">
-        <v>4.35</v>
+        <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>56519861190</v>
+        <v>5833682730</v>
       </c>
       <c r="P5" t="n">
-        <v>22450</v>
+        <v>13670</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>7060</v>
       </c>
       <c r="R5" t="n">
-        <v>59000</v>
+        <v>-73000</v>
       </c>
       <c r="S5" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>보안 대장주로서의 기대감 및 11월 양자관련법 시행 최대 수혜 전망. 해킹 이슈와 타 보안주 흐름 언급.</t>
+          <t>위식도염 임상 3상 성공에도 불구하고 시장 규모 및 경쟁 업체 대비 호재 강도 약세. 역류성 식도염 치료제 시장의 제한적인 성장성과 주가 부진 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안주', '양자보안', '최대수혜']</t>
+          <t>['임상3상', '위식도염', '역류성']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6850</v>
+        <v>6750</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.78%</t>
+          <t>'+8.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>12701665890</v>
+        <v>13037272110</v>
       </c>
       <c r="P6" t="n">
         <v>16620</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7220</v>
+        <v>7030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.73%</t>
+          <t>'+5.87%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="n">
         <v>0.85</v>
@@ -1070,7 +1070,7 @@
         <v>0.9</v>
       </c>
       <c r="O7" t="n">
-        <v>25383994415</v>
+        <v>26592312465</v>
       </c>
       <c r="P7" t="n">
         <v>9820</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>594억 규모 공급 계약 체결 사실과 함께 주포의 움직임, 유통 물량 관련 언급. BPS 13300원 기준으로의 하단 지지력 기대.</t>
+          <t>미국 시장의 영향 및 594억 공급계약 공시 기반의 상승 기대. 주포의 움직임과 유통 물량 주목.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공급계약', 'BPS', '주포']</t>
+          <t>['공급계약', '주포', '유통 물량']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9200</v>
+        <v>9020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+7.23%</t>
+          <t>'+5.13%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="H8" t="n">
         <v>2.67</v>
@@ -1162,7 +1162,7 @@
         <v>2.66</v>
       </c>
       <c r="O8" t="n">
-        <v>21738558540</v>
+        <v>22756377620</v>
       </c>
       <c r="P8" t="n">
         <v>19270</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>내년 조단위 매출 및 광통신 사업 가세 가능성 언급. 와이캅 칩 설계/생산 관련 내용과 인텔 어닝쇼크 영향 분석.</t>
+          <t>서울반도체와 연계한 광통신 사업 확장 및 칩 설계/생산 가능성 제시. 신기술에 대한 기대감과 외국인 매도세 속 투자자들의 엇갈린 반응.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '칩설계', '매출']</t>
+          <t>['광통신', '칩설계', '신기술']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15860</v>
+        <v>29350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.87%</t>
+          <t>'+4.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.9</v>
+        <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="H9" t="n">
-        <v>7.15</v>
+        <v>4.69</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14980</v>
+        <v>28050</v>
       </c>
       <c r="K9" t="n">
-        <v>14980</v>
+        <v>27850</v>
       </c>
       <c r="L9" t="n">
-        <v>16150</v>
+        <v>30400</v>
       </c>
       <c r="M9" t="n">
-        <v>14610</v>
+        <v>27650</v>
       </c>
       <c r="N9" t="n">
-        <v>8.050000000000001</v>
+        <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>35234397975</v>
+        <v>91812575925</v>
       </c>
       <c r="P9" t="n">
-        <v>49800</v>
+        <v>50600</v>
       </c>
       <c r="Q9" t="n">
-        <v>8180</v>
+        <v>13210</v>
       </c>
       <c r="R9" t="n">
-        <v>114000</v>
+        <v>-64000</v>
       </c>
       <c r="S9" t="n">
-        <v>26000</v>
+        <v>41000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 '루닛 인사이트 리스크' 미 FDA 승인 신청 및 췌장암 검사 FDA 허가 신청 관련 호재. AI 신약개발 기대주로 NH투자증권 주목.</t>
+          <t>로봇 부품(엑추에이터) 신규 진입 및 휴머노이드 로봇 손 관련 뉴스로 상승 기대감 형성. 투자자 심리는 긍정적이나, 실제 주가 움직임에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA승인', 'AI신약', '헬스케어']</t>
+          <t>['로봇손', '엑추에이터', '휴머노이드']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29300</v>
+        <v>15390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+2.74%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.36</v>
+        <v>-0.9</v>
       </c>
       <c r="E10" t="n">
+        <v>51</v>
+      </c>
+      <c r="F10" t="n">
         <v>41</v>
       </c>
-      <c r="F10" t="n">
-        <v>30</v>
-      </c>
       <c r="G10" t="n">
-        <v>151</v>
+        <v>228</v>
       </c>
       <c r="H10" t="n">
-        <v>4.69</v>
+        <v>7.15</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>28050</v>
+        <v>14980</v>
       </c>
       <c r="K10" t="n">
-        <v>27850</v>
+        <v>14980</v>
       </c>
       <c r="L10" t="n">
-        <v>30400</v>
+        <v>16150</v>
       </c>
       <c r="M10" t="n">
-        <v>27650</v>
+        <v>14610</v>
       </c>
       <c r="N10" t="n">
-        <v>5.05</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>89068246650</v>
+        <v>37298471610</v>
       </c>
       <c r="P10" t="n">
-        <v>50600</v>
+        <v>49800</v>
       </c>
       <c r="Q10" t="n">
-        <v>13210</v>
+        <v>8180</v>
       </c>
       <c r="R10" t="n">
-        <v>-64000</v>
+        <v>114000</v>
       </c>
       <c r="S10" t="n">
-        <v>41000</v>
+        <v>26000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>로봇손 관련 신규 사업 진출 및 정밀 엑추에이터 시장 진입 소식에 따른 상승 기대. 계단식 상승 및 기관 매수세 확인.</t>
+          <t>미국 FDA 승인 신청 및 AI 신약개발 기대감 언급. 2027년 유망주로 NH투자증권이 5,000억 원 가치 평가. 주가 상승에 대한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['로봇손', '엑추에이터', '기관매수']</t>
+          <t>['AI신약개발', 'FDA승인', '유방암']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49850</v>
+        <v>50300</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.53%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>69</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H11" t="n">
         <v>23.82</v>
@@ -1438,7 +1438,7 @@
         <v>24.64</v>
       </c>
       <c r="O11" t="n">
-        <v>36279312025</v>
+        <v>37801336600</v>
       </c>
       <c r="P11" t="n">
         <v>97900</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>최대 실적 발표에도 불구하고 주가 상승 미미. TC본더 매출 본격화 및 공매도 쇼트 스퀴즈 기대. 저평가된 PER 및 글로벌 수요 증가 긍정적 요인.</t>
+          <t>사상 최대 실적 발표에도 불구하고 주가 부진. TC본더 매출 본격화 및 공매도 세력에 대한 경계.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15830</v>
+        <v>15870</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.95%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
         <v>187</v>
@@ -1530,7 +1530,7 @@
         <v>28.07</v>
       </c>
       <c r="O12" t="n">
-        <v>26344332380</v>
+        <v>28057040025</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 조선주 폭등 대비 국내 조선주 기회 언급. 야간 선물 하락 및 신용 물량 출회 우려. 증권사 리포트 및 기대감 반영. 단기 투자자 경계.</t>
+          <t>미국 조선주 상승과 대비되는 국내 조선주 흐름에 대한 아쉬움. 연기금 및 기관의 매수 기대감.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선주', '기회', '증권사 리포트']</t>
+          <t>['조선주', '연기금', '기관']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60900</v>
+        <v>61200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.03%</t>
+          <t>'-2.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="H13" t="n">
         <v>41.76</v>
@@ -1622,7 +1622,7 @@
         <v>41.55</v>
       </c>
       <c r="O13" t="n">
-        <v>46081455900</v>
+        <v>48863475600</v>
       </c>
       <c r="P13" t="n">
         <v>67300</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 속 삼성E&amp;A 상승 기대. 자사주 취득 및 LOA 본계약 체결 공시 이슈. 중동 대규모 수주 공시 시 주가 급등 전망.</t>
+          <t>반도체 섹터 부진 속 삼성E&amp;A의 상승 기대. 2월 LOA 본계약 체결 공시 및 중동 대규모 수주 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['자사주 취득', 'LOA', '대규모 수주']</t>
+          <t>['LOA', '수주', '반도체']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54500</v>
+        <v>54600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.88%</t>
+          <t>'-3.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.2</v>
       </c>
       <c r="E14" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F14" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G14" t="n">
-        <v>672</v>
+        <v>686</v>
       </c>
       <c r="H14" t="n">
         <v>22.14</v>
@@ -1714,7 +1714,7 @@
         <v>22.34</v>
       </c>
       <c r="O14" t="n">
-        <v>42644780800</v>
+        <v>44501745550</v>
       </c>
       <c r="P14" t="n">
         <v>139200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11030</v>
+        <v>11060</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.08%</t>
+          <t>'-4.82%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.13</v>
       </c>
       <c r="E15" t="n">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="F15" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G15" t="n">
-        <v>823</v>
+        <v>858</v>
       </c>
       <c r="H15" t="n">
         <v>9.73</v>
@@ -1806,7 +1806,7 @@
         <v>9.6</v>
       </c>
       <c r="O15" t="n">
-        <v>32192405765</v>
+        <v>33415881270</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>219250</v>
+        <v>219000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.50%</t>
+          <t>'-5.60%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="G16" t="n">
-        <v>1242</v>
+        <v>1223</v>
       </c>
       <c r="H16" t="n">
         <v>46.17</v>
@@ -1898,7 +1898,7 @@
         <v>46.19</v>
       </c>
       <c r="O16" t="n">
-        <v>1331571653750</v>
+        <v>1396116687500</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>노조의 주가 하락 기도 및 이재용 회장의 증여세 관련 비판. 주가 하락 시 이익을 보는 회장 체제에 대한 의문 제기. 미국 상장 시 비교 및 국내 증시 상황 비판.</t>
+          <t>이재용 증여세 및 노조 관련 부정적 언급과 함께 주가 하락에 대한 불만 표출. 외인의 매도세 지속.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13960</v>
+        <v>13980</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.12%</t>
+          <t>'-6.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G17" t="n">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="H17" t="n">
         <v>3.13</v>
@@ -1990,7 +1990,7 @@
         <v>3.33</v>
       </c>
       <c r="O17" t="n">
-        <v>27098000990</v>
+        <v>28214534800</v>
       </c>
       <c r="P17" t="n">
         <v>31500</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신주 급락 및 마벨 14% 폭락 영향으로 인한 조정 예상. 정부 및 청와대 정책 기대감 언급.</t>
+          <t>광통신 관련주로 묶여 있으나, 루멘텀 홀딩스 등 연관 기업들의 주가 변동성과 국내 시장 부진으로 인한 투자 심리 위축. 목표가 제시에도 불구하고 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '조정', '정책']</t>
+          <t>['광통신', '루멘텀', '특허']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21850</v>
+        <v>21950</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-7.42%</t>
+          <t>'-6.99%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="F18" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G18" t="n">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="H18" t="n">
         <v>11.6</v>
@@ -2082,7 +2082,7 @@
         <v>12.23</v>
       </c>
       <c r="O18" t="n">
-        <v>54523720375</v>
+        <v>56786274850</v>
       </c>
       <c r="P18" t="n">
         <v>59300</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7290</v>
+        <v>7280</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.72%</t>
+          <t>'-7.85%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2174,7 +2174,7 @@
         <v>0.42</v>
       </c>
       <c r="O19" t="n">
-        <v>12686255615</v>
+        <v>12923600145</v>
       </c>
       <c r="P19" t="n">
         <v>10300</v>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1389000</v>
+        <v>1398000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.98%</t>
+          <t>'-8.39%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="G20" t="n">
-        <v>1082</v>
+        <v>1123</v>
       </c>
       <c r="H20" t="n">
         <v>48.72</v>
@@ -2266,7 +2266,7 @@
         <v>48.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1742693169000</v>
+        <v>1861783388000</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 주가 하락 원인 분석 및 비판. 외인 기관의 매도세 지속 및 단기 투자 대응 강조. 계단식 하락 및 개미 투자자 피해 우려.</t>
+          <t>주가 하락에 대한 정치적 요인 및 외국인 투자자 비판. 단기적인 대응과 장기 투자에 대한 회의감.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '외인 기관', '계단식 하락']</t>
+          <t>['정치적 요인', '외국인', '주가 하락']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>118400</v>
+        <v>118900</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-14.33%</t>
+          <t>'-13.97%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.26</v>
       </c>
       <c r="E21" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="H21" t="n">
         <v>14.2</v>
@@ -2358,7 +2358,7 @@
         <v>14.46</v>
       </c>
       <c r="O21" t="n">
-        <v>84004106900</v>
+        <v>90474323450</v>
       </c>
       <c r="P21" t="n">
         <v>198000</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>실적 발표 전 급격한 주가 하락에 대한 의문 제기. SK하이닉스 소부장 물량 확대 언급. 수급 불안 및 외인 매도 지속. 실적 사전 인지 가능성 시사.</t>
+          <t>급격한 주가 하락에 대한 불만. 실적 발표 전 주가 하락에 대한 의구심 및 외국인 수급 불안.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['실적', '주가 하락', '외인 매도']</t>
+          <t>['실적', '주가 하락', '수급']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13590</v>
+        <v>13610</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-20.06%</t>
+          <t>'-19.94%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="H22" t="n">
         <v>0.66</v>
@@ -2450,7 +2450,7 @@
         <v>0.65</v>
       </c>
       <c r="O22" t="n">
-        <v>25173086740</v>
+        <v>25655104550</v>
       </c>
       <c r="P22" t="n">
         <v>28800</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>마이크론 퀠테스트 통과 및 반도체 생산량 3배 증가 소식 기반으로 보호예수 물량 해제 후 상승 기대. 초품절주 언급.</t>
+          <t>보호예수 해제 물량 부담 및 반도체 업황 부진으로 인한 급락. 마이크론 퀠테스트 통과에도 불구하고 기술적 반등 부재 및 기관/외인 동반 매도세.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['퀠테스트', '보호예수', '반도체']</t>
+          <t>['보호예수', '퀠테스트', '반도체']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1845</v>
+        <v>1855</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-28.35%</t>
+          <t>'-27.96%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2542,7 +2542,7 @@
         <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>5857928098</v>
+        <v>5931280782</v>
       </c>
       <c r="P23" t="n">
         <v>5700</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>주가 폭락 지속, 하한가 우려. 실적 부진 언급. 외국인 대량 순매수 이유 불명확.</t>
+          <t>급락 및 거래정지 가능성 언급, 실적 부진과 로봇 관련 이슈에 대한 부정적 전망. 외국인 매수세 유입에도 불구하고 투자자들의 혼란과 불안감 가중.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['폭락', '실적', '외국인']</t>
+          <t>['거래정지', '실적부진', '로봇']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10360</v>
+        <v>10790</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-30.93%</t>
+          <t>'-28.07%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="F24" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G24" t="n">
-        <v>272</v>
+        <v>346</v>
       </c>
       <c r="H24" t="n">
         <v>3.05</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>83295262155</v>
+        <v>85276099480</v>
       </c>
       <c r="P24" t="n">
         <v>12700</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>실내 골프 사업 성장 가능성 언급. 상장 후 손바뀜 및 거래량 증가. 인텔리빅스와 비교 시 높은 순이익 및 현금 보유량 강조. 초기 상승 후 하락 마감.</t>
+          <t>상장 초기 급격한 하락 후 반등 시도. 인텔리빅스와의 비교를 통한 저평가 가능성 언급.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['실내 골프', '손바뀜', '순이익']</t>
+          <t>['상장', '반등', '인텔리빅스']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20261030_10.xlsx
+++ b/data/trending_integrated_20261030_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16670</v>
+        <v>17070</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+85.22%</t>
+          <t>'+89.67%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="F2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G2" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -604,19 +604,19 @@
         <v>21700</v>
       </c>
       <c r="M2" t="n">
-        <v>16510</v>
+        <v>16450</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>234153725275</v>
+        <v>244851320245</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
       </c>
       <c r="Q2" t="n">
-        <v>16510</v>
+        <v>16450</v>
       </c>
       <c r="R2" t="n">
         <v>-161000</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주의 높은 변동성에 대한 우려. 단기 급등 후 급락하는 흐름에 대한 부정적 전망.</t>
+          <t>신규 상장주로서 변동성이 매우 크며, 급등 후 급락하는 패턴 반복. 명확한 팩트 기반 분석보다는 단기 차익 거래 심리 강함.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장주', '변동성', '급락']</t>
+          <t>['신규 상장주', '변동성', '단타']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>진양화학</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19680</v>
+        <v>2840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.20%</t>
+          <t>'+15.92%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.75</v>
+        <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>0.79</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16650</v>
+        <v>2450</v>
       </c>
       <c r="K3" t="n">
-        <v>16830</v>
+        <v>2460</v>
       </c>
       <c r="L3" t="n">
-        <v>19690</v>
+        <v>3110</v>
       </c>
       <c r="M3" t="n">
-        <v>16750</v>
+        <v>2335</v>
       </c>
       <c r="N3" t="n">
-        <v>4.35</v>
+        <v>0.63</v>
       </c>
       <c r="O3" t="n">
-        <v>65534977505</v>
+        <v>8998851404</v>
       </c>
       <c r="P3" t="n">
-        <v>22450</v>
+        <v>3170</v>
       </c>
       <c r="Q3" t="n">
-        <v>6320</v>
+        <v>880</v>
       </c>
       <c r="R3" t="n">
-        <v>59000</v>
+        <v>38000</v>
       </c>
       <c r="S3" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>양자암호화폐 관련 법 시행에 따른 수혜 기대감. 보안 대장주로서의 입지 강화 및 기관 매수세 유입.</t>
+          <t>차기 대선 테마주 관련 언급. 오세훈, 이재명 관련 정치 테마로 분류되나, 주가 상승 근거는 미약.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['양자암호', '보안', '기관']</t>
+          <t>['대선 테마주', '오세훈', '이재명']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>051630</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12930</v>
+        <v>19170</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.45%</t>
+          <t>'+15.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>-0.75</v>
       </c>
       <c r="E4" t="n">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="G4" t="n">
-        <v>617</v>
+        <v>97</v>
       </c>
       <c r="H4" t="n">
-        <v>15.04</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11200</v>
+        <v>16650</v>
       </c>
       <c r="K4" t="n">
-        <v>13500</v>
+        <v>16830</v>
       </c>
       <c r="L4" t="n">
-        <v>13710</v>
+        <v>19750</v>
       </c>
       <c r="M4" t="n">
-        <v>12100</v>
+        <v>16750</v>
       </c>
       <c r="N4" t="n">
-        <v>15.08</v>
+        <v>4.35</v>
       </c>
       <c r="O4" t="n">
-        <v>34123304890</v>
+        <v>74625093745</v>
       </c>
       <c r="P4" t="n">
-        <v>18960</v>
+        <v>22450</v>
       </c>
       <c r="Q4" t="n">
-        <v>5730</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-260000</v>
+        <v>59000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 시장 석권 가능성 언급. 강력한 기술력 기반의 긍정적 주가 전망 및 공매도 세력에 대한 경고.</t>
+          <t>바이낸스, 빗썸 등 거래소 해킹 연이어 발생하며 보안주 관심 집중. 11월 양자 관련법 시행 시 최대 수혜 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['백색LED', '희토류', '게임체인져']</t>
+          <t>['보안주', '양자암호', '해킹']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8740</v>
+        <v>12850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.51%</t>
+          <t>'+14.73%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.37</v>
+        <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>623</v>
       </c>
       <c r="H5" t="n">
-        <v>13.29</v>
+        <v>15.04</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7700</v>
+        <v>11200</v>
       </c>
       <c r="K5" t="n">
-        <v>9360</v>
+        <v>13500</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>13710</v>
       </c>
       <c r="M5" t="n">
-        <v>8610</v>
+        <v>12100</v>
       </c>
       <c r="N5" t="n">
-        <v>12.92</v>
+        <v>15.08</v>
       </c>
       <c r="O5" t="n">
-        <v>5833682730</v>
+        <v>35013954230</v>
       </c>
       <c r="P5" t="n">
-        <v>13670</v>
+        <v>18960</v>
       </c>
       <c r="Q5" t="n">
-        <v>7060</v>
+        <v>5730</v>
       </c>
       <c r="R5" t="n">
-        <v>-73000</v>
+        <v>-260000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>위식도염 임상 3상 성공에도 불구하고 시장 규모 및 경쟁 업체 대비 호재 강도 약세. 역류성 식도염 치료제 시장의 제한적인 성장성과 주가 부진 전망.</t>
+          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 백색 LED 시장 석권 전망. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['임상3상', '위식도염', '역류성']</t>
+          <t>['백색LED', '희토류', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,77 +924,77 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>상지건설</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6750</v>
+        <v>8780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.17%</t>
+          <t>'+14.03%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="E6" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>13.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6240</v>
+        <v>7700</v>
       </c>
       <c r="K6" t="n">
-        <v>6700</v>
+        <v>9360</v>
       </c>
       <c r="L6" t="n">
-        <v>7670</v>
+        <v>9500</v>
       </c>
       <c r="M6" t="n">
-        <v>6330</v>
+        <v>8610</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12.92</v>
       </c>
       <c r="O6" t="n">
-        <v>13037272110</v>
+        <v>5949563940</v>
       </c>
       <c r="P6" t="n">
-        <v>16620</v>
+        <v>13670</v>
       </c>
       <c r="Q6" t="n">
-        <v>4600</v>
+        <v>7060</v>
       </c>
       <c r="R6" t="n">
-        <v>1000</v>
+        <v>-73000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>연속 상승 후 하락세 전환 및 유상증자 이후 전망 부정적. 재탕 삼탕 뉴스에 대한 의구심 표현.</t>
+          <t>역류성 식도염 임상 3상 성공에 대한 기대감 약화 및 재료 소멸 가능성 언급. 시장 규모 및 경쟁 업체 대비 호재 미미.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유상증자', '하락세', '건설']</t>
+          <t>['임상 3상', '역류성 식도염', '재료 소멸']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042940</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>상지건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7030</v>
+        <v>6570</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.87%</t>
+          <t>'+5.29%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="H7" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6640</v>
+        <v>6240</v>
       </c>
       <c r="K7" t="n">
-        <v>7210</v>
+        <v>6700</v>
       </c>
       <c r="L7" t="n">
-        <v>7500</v>
+        <v>7670</v>
       </c>
       <c r="M7" t="n">
-        <v>6730</v>
+        <v>6330</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>26592312465</v>
+        <v>13237078540</v>
       </c>
       <c r="P7" t="n">
-        <v>9820</v>
+        <v>16620</v>
       </c>
       <c r="Q7" t="n">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="R7" t="n">
-        <v>-46000</v>
+        <v>1000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 시장의 영향 및 594억 공급계약 공시 기반의 상승 기대. 주포의 움직임과 유통 물량 주목.</t>
+          <t>지수 급락 상황 속 건설 대장주로서의 역할 기대. 유상증자 및 재탕 뉴스에 대한 부정적 시각 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공급계약', '주포', '유통 물량']</t>
+          <t>['건설대장주', '유상증자', '재료']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>042940</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9020</v>
+        <v>51400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.13%</t>
+          <t>'+4.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.82</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H8" t="n">
-        <v>2.67</v>
+        <v>23.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>8580</v>
+        <v>49100</v>
       </c>
       <c r="K8" t="n">
-        <v>11090</v>
+        <v>49450</v>
       </c>
       <c r="L8" t="n">
-        <v>11150</v>
+        <v>52000</v>
       </c>
       <c r="M8" t="n">
-        <v>8400</v>
+        <v>48050</v>
       </c>
       <c r="N8" t="n">
-        <v>2.66</v>
+        <v>24.64</v>
       </c>
       <c r="O8" t="n">
-        <v>22756377620</v>
+        <v>40250066850</v>
       </c>
       <c r="P8" t="n">
-        <v>19270</v>
+        <v>97900</v>
       </c>
       <c r="Q8" t="n">
-        <v>2135</v>
+        <v>30950</v>
       </c>
       <c r="R8" t="n">
-        <v>-341000</v>
+        <v>-85000</v>
       </c>
       <c r="S8" t="n">
-        <v>-2000</v>
+        <v>36000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>서울반도체와 연계한 광통신 사업 확장 및 칩 설계/생산 가능성 제시. 신기술에 대한 기대감과 외국인 매도세 속 투자자들의 엇갈린 반응.</t>
+          <t>역대 최대 실적 발표 및 TC본더 매출 본격화 긍정적. 사이버 보안 수혜 기대. 공매도 세력과의 대립 양상.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['광통신', '칩설계', '신기술']</t>
+          <t>['실적', 'TC본더', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29350</v>
+        <v>29300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.63%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="H9" t="n">
         <v>4.69</v>
@@ -1254,7 +1254,7 @@
         <v>5.05</v>
       </c>
       <c r="O9" t="n">
-        <v>91812575925</v>
+        <v>94311908375</v>
       </c>
       <c r="P9" t="n">
         <v>50600</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>로봇 부품(엑추에이터) 신규 진입 및 휴머노이드 로봇 손 관련 뉴스로 상승 기대감 형성. 투자자 심리는 긍정적이나, 실제 주가 움직임에 대한 의문 제기.</t>
+          <t>이재용 로봇손 관련 부품(엑츄에이터) 시장 신규 진입 소식. 3만원대 돌파 시 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇손', '엑추에이터', '휴머노이드']</t>
+          <t>['로봇손', '엑츄에이터', '휴머노이드']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15390</v>
+        <v>6900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.74%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.9</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>228</v>
+        <v>36</v>
       </c>
       <c r="H10" t="n">
-        <v>7.15</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14980</v>
+        <v>6640</v>
       </c>
       <c r="K10" t="n">
-        <v>14980</v>
+        <v>7210</v>
       </c>
       <c r="L10" t="n">
-        <v>16150</v>
+        <v>7500</v>
       </c>
       <c r="M10" t="n">
-        <v>14610</v>
+        <v>6730</v>
       </c>
       <c r="N10" t="n">
-        <v>8.050000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="O10" t="n">
-        <v>37298471610</v>
+        <v>27145224985</v>
       </c>
       <c r="P10" t="n">
-        <v>49800</v>
+        <v>9820</v>
       </c>
       <c r="Q10" t="n">
-        <v>8180</v>
+        <v>4000</v>
       </c>
       <c r="R10" t="n">
-        <v>114000</v>
+        <v>-46000</v>
       </c>
       <c r="S10" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 FDA 승인 신청 및 AI 신약개발 기대감 언급. 2027년 유망주로 NH투자증권이 5,000억 원 가치 평가. 주가 상승에 대한 긍정적 전망.</t>
+          <t>미국 시장 흐름에 따른 양지사 급등 언급. 594억 규모 공급 계약 확인 및 유통 물량 관련 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI신약개발', 'FDA승인', '유방암']</t>
+          <t>['공급계약', '테마주', '유통물량']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50300</v>
+        <v>15440</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.82</v>
+        <v>-0.9</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="H11" t="n">
-        <v>23.82</v>
+        <v>7.15</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>49100</v>
+        <v>14980</v>
       </c>
       <c r="K11" t="n">
-        <v>49450</v>
+        <v>14980</v>
       </c>
       <c r="L11" t="n">
-        <v>52000</v>
+        <v>16150</v>
       </c>
       <c r="M11" t="n">
-        <v>48050</v>
+        <v>14610</v>
       </c>
       <c r="N11" t="n">
-        <v>24.64</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>37801336600</v>
+        <v>38370181735</v>
       </c>
       <c r="P11" t="n">
-        <v>97900</v>
+        <v>49800</v>
       </c>
       <c r="Q11" t="n">
-        <v>30950</v>
+        <v>8180</v>
       </c>
       <c r="R11" t="n">
-        <v>-85000</v>
+        <v>114000</v>
       </c>
       <c r="S11" t="n">
-        <v>36000</v>
+        <v>26000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>사상 최대 실적 발표에도 불구하고 주가 부진. TC본더 매출 본격화 및 공매도 세력에 대한 경계.</t>
+          <t>유방암 위험 예측 솔루션 '루닛 인사이트 리스크' 미 FDA 승인 신청. AI 신약개발 관련 높은 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', '공매도']</t>
+          <t>['AI 신약개발', 'FDA 승인', '유방암']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,77 +1476,77 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15870</v>
+        <v>8840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.95%</t>
+          <t>'+3.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="H12" t="n">
-        <v>28.13</v>
+        <v>2.67</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15720</v>
+        <v>8580</v>
       </c>
       <c r="K12" t="n">
-        <v>15420</v>
+        <v>11090</v>
       </c>
       <c r="L12" t="n">
-        <v>16050</v>
+        <v>11150</v>
       </c>
       <c r="M12" t="n">
-        <v>15320</v>
+        <v>8400</v>
       </c>
       <c r="N12" t="n">
-        <v>28.07</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>28057040025</v>
+        <v>23371637505</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>19270</v>
       </c>
       <c r="Q12" t="n">
-        <v>15320</v>
+        <v>2135</v>
       </c>
       <c r="R12" t="n">
-        <v>231000</v>
+        <v>-341000</v>
       </c>
       <c r="S12" t="n">
-        <v>14000</v>
+        <v>-2000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 조선주 상승과 대비되는 국내 조선주 흐름에 대한 아쉬움. 연기금 및 기관의 매수 기대감.</t>
+          <t>서울반도체와의 비교 및 영업이익 역전 기대. 내년 조단위 매출 및 광통신 사업 확장 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['조선주', '연기금', '기관']</t>
+          <t>['광통신', '영업이익', '매출']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61200</v>
+        <v>15870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.55%</t>
+          <t>'+0.95%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="E13" t="n">
+        <v>79</v>
+      </c>
+      <c r="F13" t="n">
         <v>51</v>
       </c>
-      <c r="F13" t="n">
-        <v>30</v>
-      </c>
       <c r="G13" t="n">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="H13" t="n">
-        <v>41.76</v>
+        <v>28.13</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>62800</v>
+        <v>15720</v>
       </c>
       <c r="K13" t="n">
-        <v>62300</v>
+        <v>15420</v>
       </c>
       <c r="L13" t="n">
-        <v>62800</v>
+        <v>16050</v>
       </c>
       <c r="M13" t="n">
-        <v>60700</v>
+        <v>15320</v>
       </c>
       <c r="N13" t="n">
-        <v>41.55</v>
+        <v>28.07</v>
       </c>
       <c r="O13" t="n">
-        <v>48863475600</v>
+        <v>29609593580</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>15320</v>
       </c>
       <c r="R13" t="n">
-        <v>69000</v>
+        <v>231000</v>
       </c>
       <c r="S13" t="n">
-        <v>-10000</v>
+        <v>14000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 섹터 부진 속 삼성E&amp;A의 상승 기대. 2월 LOA 본계약 체결 공시 및 중동 대규모 수주 가능성 언급.</t>
+          <t>미국 조선주 강세와 비교하며 조선 섹터 기회 언급. 증권사 리포트 긍정적 전망. 대규모 수주 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['LOA', '수주', '반도체']</t>
+          <t>['조선주', '수주 기대', '증권사 리포트']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>54600</v>
+        <v>61100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-2.71%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.2</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="G14" t="n">
-        <v>686</v>
+        <v>220</v>
       </c>
       <c r="H14" t="n">
-        <v>22.14</v>
+        <v>41.76</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>56700</v>
+        <v>62800</v>
       </c>
       <c r="K14" t="n">
-        <v>55500</v>
+        <v>62300</v>
       </c>
       <c r="L14" t="n">
-        <v>55900</v>
+        <v>62800</v>
       </c>
       <c r="M14" t="n">
-        <v>54000</v>
+        <v>60700</v>
       </c>
       <c r="N14" t="n">
-        <v>22.34</v>
+        <v>41.55</v>
       </c>
       <c r="O14" t="n">
-        <v>44501745550</v>
+        <v>51416847700</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>67300</v>
       </c>
       <c r="Q14" t="n">
-        <v>53400</v>
+        <v>23150</v>
       </c>
       <c r="R14" t="n">
-        <v>-85000</v>
+        <v>69000</v>
       </c>
       <c r="S14" t="n">
-        <v>-58000</v>
+        <v>-10000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 전망. 체코 원전 사업 관련 비판과 함께 원전주 상승 가능성 언급. 실적과 무관한 주가 움직임에 대한 불만.</t>
+          <t>반도체 시장과 대비되는 긍정적 전망. 자사주 취득, 중동 대규모 수주 공시 기대감. 외인 순매수 긍정적 신호.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['SMR', '수주', '실적']</t>
+          <t>['자사주 취득', '수주 공시', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11060</v>
+        <v>54500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.82%</t>
+          <t>'-3.88%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.13</v>
+        <v>-0.2</v>
       </c>
       <c r="E15" t="n">
-        <v>256</v>
+        <v>214</v>
       </c>
       <c r="F15" t="n">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="G15" t="n">
-        <v>858</v>
+        <v>695</v>
       </c>
       <c r="H15" t="n">
-        <v>9.73</v>
+        <v>22.14</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>11620</v>
+        <v>56700</v>
       </c>
       <c r="K15" t="n">
-        <v>11300</v>
+        <v>55500</v>
       </c>
       <c r="L15" t="n">
-        <v>11470</v>
+        <v>55900</v>
       </c>
       <c r="M15" t="n">
-        <v>10960</v>
+        <v>54000</v>
       </c>
       <c r="N15" t="n">
-        <v>9.6</v>
+        <v>22.34</v>
       </c>
       <c r="O15" t="n">
-        <v>33415881270</v>
+        <v>46214269300</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>53400</v>
       </c>
       <c r="R15" t="n">
-        <v>101000</v>
+        <v>-85000</v>
       </c>
       <c r="S15" t="n">
-        <v>-32000</v>
+        <v>-58000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>한수원 갑질 거절 및 원전 관련 호재 기대감. 공매도 금지 조치와 가덕도 신공항 흑자 전환 전망으로 주가 상승 기대.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 전망. 체코 원전 사업 관련 비판과 함께 원전주 상승 가능성 언급. 실적과 무관한 주가 움직임에 대한 불만.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '가덕도', '공매도']</t>
+          <t>['SMR', '수주', '실적']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>219000</v>
+        <v>11080</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.60%</t>
+          <t>'-4.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>264</v>
       </c>
       <c r="F16" t="n">
-        <v>529</v>
+        <v>137</v>
       </c>
       <c r="G16" t="n">
-        <v>1223</v>
+        <v>889</v>
       </c>
       <c r="H16" t="n">
-        <v>46.17</v>
+        <v>9.73</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,47 +1883,47 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>232000</v>
+        <v>11620</v>
       </c>
       <c r="K16" t="n">
-        <v>223500</v>
+        <v>11300</v>
       </c>
       <c r="L16" t="n">
-        <v>229500</v>
+        <v>11470</v>
       </c>
       <c r="M16" t="n">
-        <v>219000</v>
+        <v>10960</v>
       </c>
       <c r="N16" t="n">
-        <v>46.19</v>
+        <v>9.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1396116687500</v>
+        <v>35099989245</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q16" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R16" t="n">
-        <v>1338000</v>
+        <v>101000</v>
       </c>
       <c r="S16" t="n">
-        <v>-249000</v>
+        <v>-32000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이재용 증여세 및 노조 관련 부정적 언급과 함께 주가 하락에 대한 불만 표출. 외인의 매도세 지속.</t>
+          <t>원전, 가덕도 관련 정부 정책 수혜 기대. 공매도 금지 조치 언급. 재건 사업 전망도 긍정적 요인으로 작용.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['노조', '증여세', '주가 하락']</t>
+          <t>['원전', '가덕도', '공매도 금지']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13980</v>
+        <v>218500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-6.99%</t>
+          <t>'-5.82%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E17" t="n">
-        <v>81</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>524</v>
       </c>
       <c r="G17" t="n">
-        <v>254</v>
+        <v>1230</v>
       </c>
       <c r="H17" t="n">
-        <v>3.13</v>
+        <v>46.17</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>15030</v>
+        <v>232000</v>
       </c>
       <c r="K17" t="n">
-        <v>14500</v>
+        <v>223500</v>
       </c>
       <c r="L17" t="n">
-        <v>14570</v>
+        <v>229500</v>
       </c>
       <c r="M17" t="n">
-        <v>13920</v>
+        <v>218000</v>
       </c>
       <c r="N17" t="n">
-        <v>3.33</v>
+        <v>46.19</v>
       </c>
       <c r="O17" t="n">
-        <v>28214534800</v>
+        <v>1533968500500</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>1830</v>
+        <v>94500</v>
       </c>
       <c r="R17" t="n">
-        <v>8000</v>
+        <v>1338000</v>
       </c>
       <c r="S17" t="n">
-        <v>-9000</v>
+        <v>-249000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>광통신 관련주로 묶여 있으나, 루멘텀 홀딩스 등 연관 기업들의 주가 변동성과 국내 시장 부진으로 인한 투자 심리 위축. 목표가 제시에도 불구하고 하락 가능성 언급.</t>
+          <t>이재용 증여세, 노조 행동, 정치적 리스크 등 부정적 요인 언급. 하지만 구체적인 실적이나 공시 기반 분석은 부족.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '루멘텀', '특허']</t>
+          <t>['이재용', '노조', '리스크']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21950</v>
+        <v>22150</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.99%</t>
+          <t>'-6.14%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.63</v>
       </c>
       <c r="E18" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F18" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G18" t="n">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="H18" t="n">
         <v>11.6</v>
@@ -2082,7 +2082,7 @@
         <v>12.23</v>
       </c>
       <c r="O18" t="n">
-        <v>56786274850</v>
+        <v>58996779775</v>
       </c>
       <c r="P18" t="n">
         <v>59300</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>김동원 부회장의 주가 누르기 의혹 및 구속 수사 임박 가능성 제기. 태양광 수혜 및 RE100 승인 관련 내용 포함. 주가 하락폭에 대한 강한 불만 표출.</t>
+          <t>태양광 사업 관련 긍정적 뉴스 언급 있으나, 주가 하락세에 대한 우려가 지배적. 주가 누르기 의혹 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['김동원 부회장', '주가 누르기', '태양광']</t>
+          <t>['태양광', '주가 하락', '주가 조작']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7280</v>
+        <v>14030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.85%</t>
+          <t>'-6.65%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.03</v>
+        <v>-0.2</v>
       </c>
       <c r="E19" t="n">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>87</v>
+        <v>260</v>
       </c>
       <c r="H19" t="n">
-        <v>0.39</v>
+        <v>3.13</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>7900</v>
+        <v>15030</v>
       </c>
       <c r="K19" t="n">
-        <v>7790</v>
+        <v>14500</v>
       </c>
       <c r="L19" t="n">
-        <v>8130</v>
+        <v>14570</v>
       </c>
       <c r="M19" t="n">
-        <v>7150</v>
+        <v>13920</v>
       </c>
       <c r="N19" t="n">
-        <v>0.42</v>
+        <v>3.33</v>
       </c>
       <c r="O19" t="n">
-        <v>12923600145</v>
+        <v>28997246500</v>
       </c>
       <c r="P19" t="n">
-        <v>10300</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>952</v>
+        <v>1830</v>
       </c>
       <c r="R19" t="n">
-        <v>-11000</v>
+        <v>8000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
+          <t>미국 광통신 주식 동반 상승 및 루닛 연기금 매수 언급. 3만 전고점까지 홀딩 전망.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['공급계약', '재료', '주가']</t>
+          <t>['광통신', '연기금', '전고점']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1398000</v>
+        <v>1401000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.39%</t>
+          <t>'-8.19%</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2237,10 +2237,10 @@
         <v>800</v>
       </c>
       <c r="F20" t="n">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="G20" t="n">
-        <v>1123</v>
+        <v>1114</v>
       </c>
       <c r="H20" t="n">
         <v>48.72</v>
@@ -2266,7 +2266,7 @@
         <v>48.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1861783388000</v>
+        <v>1967930374000</v>
       </c>
       <c r="P20" t="n">
         <v>2987000</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 정치적 요인 및 외국인 투자자 비판. 단기적인 대응과 장기 투자에 대한 회의감.</t>
+          <t>정치적 이슈와 함께 전반적인 시장 하락세에 대한 부정적 전망. 외국인 투자자 관점 언급. 단기 차익 실현 권장.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['정치적 요인', '외국인', '주가 하락']</t>
+          <t>['시장 하락', '외국인', '단기 매매']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2311,83 +2311,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>118900</v>
+        <v>7220</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-13.97%</t>
+          <t>'-8.61%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.26</v>
+        <v>-0.03</v>
       </c>
       <c r="E21" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>163</v>
+        <v>87</v>
       </c>
       <c r="H21" t="n">
-        <v>14.2</v>
+        <v>0.39</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>138200</v>
+        <v>7900</v>
       </c>
       <c r="K21" t="n">
-        <v>132600</v>
+        <v>7790</v>
       </c>
       <c r="L21" t="n">
-        <v>132900</v>
+        <v>8130</v>
       </c>
       <c r="M21" t="n">
-        <v>118000</v>
+        <v>7150</v>
       </c>
       <c r="N21" t="n">
-        <v>14.46</v>
+        <v>0.42</v>
       </c>
       <c r="O21" t="n">
-        <v>90474323450</v>
+        <v>13260798115</v>
       </c>
       <c r="P21" t="n">
-        <v>198000</v>
+        <v>10300</v>
       </c>
       <c r="Q21" t="n">
-        <v>36450</v>
+        <v>952</v>
       </c>
       <c r="R21" t="n">
-        <v>-162000</v>
+        <v>-11000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>급격한 주가 하락에 대한 불만. 실적 발표 전 주가 하락에 대한 의구심 및 외국인 수급 불안.</t>
+          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['실적', '주가 하락', '수급']</t>
+          <t>['공급계약', '재료', '주가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,77 +2396,77 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13610</v>
+        <v>118400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-19.94%</t>
+          <t>'-14.33%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.01</v>
+        <v>-0.26</v>
       </c>
       <c r="E22" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>103</v>
+        <v>182</v>
       </c>
       <c r="H22" t="n">
-        <v>0.66</v>
+        <v>14.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>17000</v>
+        <v>138200</v>
       </c>
       <c r="K22" t="n">
-        <v>14000</v>
+        <v>132600</v>
       </c>
       <c r="L22" t="n">
-        <v>14900</v>
+        <v>132900</v>
       </c>
       <c r="M22" t="n">
-        <v>13260</v>
+        <v>118000</v>
       </c>
       <c r="N22" t="n">
-        <v>0.65</v>
+        <v>14.46</v>
       </c>
       <c r="O22" t="n">
-        <v>25655104550</v>
+        <v>94826762950</v>
       </c>
       <c r="P22" t="n">
-        <v>28800</v>
+        <v>198000</v>
       </c>
       <c r="Q22" t="n">
-        <v>11550</v>
+        <v>36450</v>
       </c>
       <c r="R22" t="n">
-        <v>-7000</v>
+        <v>-162000</v>
       </c>
       <c r="S22" t="n">
-        <v>-150000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>보호예수 해제 물량 부담 및 반도체 업황 부진으로 인한 급락. 마이크론 퀠테스트 통과에도 불구하고 기술적 반등 부재 및 기관/외인 동반 매도세.</t>
+          <t>반도체 섹터 전반의 하락세 속에 급락. 실적에 대한 기대감 있으나, 주가 하락폭이 커 투자자 불안감 고조.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['보호예수', '퀠테스트', '반도체']</t>
+          <t>['반도체', '실적', '주가 하락']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>353200</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>벡트로보틱스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1855</v>
+        <v>13510</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-27.96%</t>
+          <t>'-20.53%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.45</v>
+        <v>0.01</v>
       </c>
       <c r="E23" t="n">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="G23" t="n">
-        <v>28</v>
+        <v>106</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>0.66</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,51 +2527,51 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2575</v>
+        <v>17000</v>
       </c>
       <c r="K23" t="n">
-        <v>1960</v>
+        <v>14000</v>
       </c>
       <c r="L23" t="n">
-        <v>2005</v>
+        <v>14900</v>
       </c>
       <c r="M23" t="n">
-        <v>1811</v>
+        <v>13260</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>0.65</v>
       </c>
       <c r="O23" t="n">
-        <v>5931280782</v>
+        <v>26107844565</v>
       </c>
       <c r="P23" t="n">
-        <v>5700</v>
+        <v>28800</v>
       </c>
       <c r="Q23" t="n">
-        <v>1401</v>
+        <v>11550</v>
       </c>
       <c r="R23" t="n">
-        <v>219000</v>
+        <v>-7000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-150000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>급락 및 거래정지 가능성 언급, 실적 부진과 로봇 관련 이슈에 대한 부정적 전망. 외국인 매수세 유입에도 불구하고 투자자들의 혼란과 불안감 가중.</t>
+          <t>보호예수 해제 및 마이크론 퀠테스트 통과 관련 기대감에도 불구하고 주가 하락. ASML 장비 수주 공시 시 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['거래정지', '실적부진', '로봇']</t>
+          <t>['보호예수', '마이크론', 'ASML']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>457600</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10790</v>
+        <v>10730</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-28.07%</t>
+          <t>'-28.47%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="G24" t="n">
-        <v>346</v>
+        <v>410</v>
       </c>
       <c r="H24" t="n">
         <v>3.05</v>
@@ -2634,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>85276099480</v>
+        <v>88084018335</v>
       </c>
       <c r="P24" t="n">
         <v>12700</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>상장 초기 급격한 하락 후 반등 시도. 인텔리빅스와의 비교를 통한 저평가 가능성 언급.</t>
+          <t>미국 유럽 실내골프 대회 개최 등 대중화 초입 단계 언급. 상장 직후 하한가에 대한 주관사 사기 의혹 제기.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['상장', '반등', '인텔리빅스']</t>
+          <t>['실내골프', '대중화', '상장']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2673,6 +2673,98 @@
       <c r="Z24" t="inlineStr">
         <is>
           <t>439270</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>벡트로보틱스</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1831</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>'-28.89%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>44</v>
+      </c>
+      <c r="F25" t="n">
+        <v>26</v>
+      </c>
+      <c r="G25" t="n">
+        <v>25</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>2575</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1811</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O25" t="n">
+        <v>6039476906</v>
+      </c>
+      <c r="P25" t="n">
+        <v>5700</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R25" t="n">
+        <v>219000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>연이은 하한가 및 거래정지 가능성 언급. 대표이사가 투자조합이며 실적 부진으로 인한 하락세 지적.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>['거래정지', '실적부진', '투자조합']</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>457600</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261030_10.xlsx
+++ b/data/trending_integrated_20261030_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17070</v>
+        <v>17380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+89.67%</t>
+          <t>'+93.11%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="F2" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="G2" t="n">
-        <v>263</v>
+        <v>320</v>
       </c>
       <c r="H2" t="n">
         <v>1.98</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>244851320245</v>
+        <v>251512479430</v>
       </c>
       <c r="P2" t="n">
         <v>21700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신규 상장주로서 변동성이 매우 크며, 급등 후 급락하는 패턴 반복. 명확한 팩트 기반 분석보다는 단기 차익 거래 심리 강함.</t>
+          <t>신규 상장주에 대한 부정적 언급이 많으며, 주가 하락 패턴에 대한 불만이 지배적. '잡주'라는 표현 사용.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신규 상장주', '변동성', '단타']</t>
+          <t>['신규 상장주', '주가 하락', '잡주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2840</v>
+        <v>2945</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+15.92%</t>
+          <t>'+20.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" t="n">
         <v>0.79</v>
@@ -702,7 +702,7 @@
         <v>0.63</v>
       </c>
       <c r="O3" t="n">
-        <v>8998851404</v>
+        <v>9187637377</v>
       </c>
       <c r="P3" t="n">
         <v>3170</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>차기 대선 테마주 관련 언급. 오세훈, 이재명 관련 정치 테마로 분류되나, 주가 상승 근거는 미약.</t>
+          <t>정치 테마주로 분류되며 차기 대권 관련 언급이 많음. 대법원 판결 및 상폐 우려 관련 부정적 전망도 혼재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['대선 테마주', '오세훈', '이재명']</t>
+          <t>['정치 테마주', '대법원 판결', '상폐 우려']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>서울반도체</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19170</v>
+        <v>12760</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.14%</t>
+          <t>'+13.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.75</v>
+        <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="G4" t="n">
-        <v>97</v>
+        <v>648</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>15.04</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16650</v>
+        <v>11200</v>
       </c>
       <c r="K4" t="n">
-        <v>16830</v>
+        <v>13500</v>
       </c>
       <c r="L4" t="n">
-        <v>19750</v>
+        <v>13710</v>
       </c>
       <c r="M4" t="n">
-        <v>16750</v>
+        <v>12100</v>
       </c>
       <c r="N4" t="n">
-        <v>4.35</v>
+        <v>15.08</v>
       </c>
       <c r="O4" t="n">
-        <v>74625093745</v>
+        <v>36511996060</v>
       </c>
       <c r="P4" t="n">
-        <v>22450</v>
+        <v>18960</v>
       </c>
       <c r="Q4" t="n">
-        <v>6320</v>
+        <v>5730</v>
       </c>
       <c r="R4" t="n">
-        <v>59000</v>
+        <v>-260000</v>
       </c>
       <c r="S4" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>바이낸스, 빗썸 등 거래소 해킹 연이어 발생하며 보안주 관심 집중. 11월 양자 관련법 시행 시 최대 수혜 전망.</t>
+          <t>희토류 없는 백색 LED 세계 최초 개발 사실 기반 상승 기대. 100억 달러 시장 석권 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['보안주', '양자암호', '해킹']</t>
+          <t>['백색 LED', '희토류 대체', '세계 최초']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,86 +832,86 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>046890</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>서울반도체</t>
+          <t>대원제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12850</v>
+        <v>8740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.73%</t>
+          <t>'+13.51%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>0.37</v>
       </c>
       <c r="E5" t="n">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>144</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>623</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
-        <v>15.04</v>
+        <v>13.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11200</v>
+        <v>7700</v>
       </c>
       <c r="K5" t="n">
-        <v>13500</v>
+        <v>9360</v>
       </c>
       <c r="L5" t="n">
-        <v>13710</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>12100</v>
+        <v>8610</v>
       </c>
       <c r="N5" t="n">
-        <v>15.08</v>
+        <v>12.92</v>
       </c>
       <c r="O5" t="n">
-        <v>35013954230</v>
+        <v>6115631730</v>
       </c>
       <c r="P5" t="n">
-        <v>18960</v>
+        <v>13670</v>
       </c>
       <c r="Q5" t="n">
-        <v>5730</v>
+        <v>7060</v>
       </c>
       <c r="R5" t="n">
-        <v>-260000</v>
+        <v>-73000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>세계 최초 희토류 없는 백색 LED 개발 및 100억 달러 백색 LED 시장 석권 전망. 공매도 관련 언급.</t>
+          <t>임상 3상 성공에도 불구하고 주가 부진. 시장 규모 및 경쟁 업체 고려 시 큰 호재 아님.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['백색LED', '희토류', '공매도']</t>
+          <t>['임상 3상', '위식도염', '시장 규모']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>046890</t>
+          <t>003220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8780</v>
+        <v>18850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+14.03%</t>
+          <t>'+13.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.37</v>
+        <v>-0.75</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H6" t="n">
-        <v>13.29</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7700</v>
+        <v>16650</v>
       </c>
       <c r="K6" t="n">
-        <v>9360</v>
+        <v>16830</v>
       </c>
       <c r="L6" t="n">
-        <v>9500</v>
+        <v>19750</v>
       </c>
       <c r="M6" t="n">
-        <v>8610</v>
+        <v>16750</v>
       </c>
       <c r="N6" t="n">
-        <v>12.92</v>
+        <v>4.35</v>
       </c>
       <c r="O6" t="n">
-        <v>5949563940</v>
+        <v>77861071460</v>
       </c>
       <c r="P6" t="n">
-        <v>13670</v>
+        <v>22450</v>
       </c>
       <c r="Q6" t="n">
-        <v>7060</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>-73000</v>
+        <v>59000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>역류성 식도염 임상 3상 성공에 대한 기대감 약화 및 재료 소멸 가능성 언급. 시장 규모 및 경쟁 업체 대비 호재 미미.</t>
+          <t>해킹 사태 및 양자 보안법 시행 관련 최대 수혜주로 언급. 기술력과 시장 지배력에 대한 긍정적 평가.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['임상 3상', '역류성 식도염', '재료 소멸']</t>
+          <t>['보안주', '양자 보안', '해킹']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>003220</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6570</v>
+        <v>6610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.29%</t>
+          <t>'+5.93%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>13237078540</v>
+        <v>13386168990</v>
       </c>
       <c r="P7" t="n">
         <v>16620</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>지수 급락 상황 속 건설 대장주로서의 역할 기대. 유상증자 및 재탕 뉴스에 대한 부정적 시각 존재.</t>
+          <t>건설 경기 전환점 및 재료 기반 상승 기대. 유상 청약율 및 시장 상황 고려 필요.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['건설대장주', '유상증자', '재료']</t>
+          <t>['건설 경기', '유상 청약', '재료']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,70 +1115,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한화비전</t>
+          <t>양지사</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>51400</v>
+        <v>7020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.68%</t>
+          <t>'+5.72%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.82</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="H8" t="n">
-        <v>23.82</v>
+        <v>0.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>49100</v>
+        <v>6640</v>
       </c>
       <c r="K8" t="n">
-        <v>49450</v>
+        <v>7210</v>
       </c>
       <c r="L8" t="n">
-        <v>52000</v>
+        <v>7500</v>
       </c>
       <c r="M8" t="n">
-        <v>48050</v>
+        <v>6730</v>
       </c>
       <c r="N8" t="n">
-        <v>24.64</v>
+        <v>0.9</v>
       </c>
       <c r="O8" t="n">
-        <v>40250066850</v>
+        <v>27761353955</v>
       </c>
       <c r="P8" t="n">
-        <v>97900</v>
+        <v>9820</v>
       </c>
       <c r="Q8" t="n">
-        <v>30950</v>
+        <v>4000</v>
       </c>
       <c r="R8" t="n">
-        <v>-85000</v>
+        <v>-46000</v>
       </c>
       <c r="S8" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>역대 최대 실적 발표 및 TC본더 매출 본격화 긍정적. 사이버 보안 수혜 기대. 공매도 세력과의 대립 양상.</t>
+          <t>미국 시장 급등에 따른 주가 상승 기대감. 594억 규모 공급 계약 사실 확인.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적', 'TC본더', '공매도']</t>
+          <t>['공급 계약', '유통 물량', '주포']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>489790</t>
+          <t>030960</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>한화비전</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29300</v>
+        <v>50900</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.46%</t>
+          <t>'+3.67%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.36</v>
+        <v>-0.82</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="H9" t="n">
-        <v>4.69</v>
+        <v>23.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28050</v>
+        <v>49100</v>
       </c>
       <c r="K9" t="n">
-        <v>27850</v>
+        <v>49450</v>
       </c>
       <c r="L9" t="n">
-        <v>30400</v>
+        <v>52000</v>
       </c>
       <c r="M9" t="n">
-        <v>27650</v>
+        <v>48050</v>
       </c>
       <c r="N9" t="n">
-        <v>5.05</v>
+        <v>24.64</v>
       </c>
       <c r="O9" t="n">
-        <v>94311908375</v>
+        <v>42241897600</v>
       </c>
       <c r="P9" t="n">
-        <v>50600</v>
+        <v>97900</v>
       </c>
       <c r="Q9" t="n">
-        <v>13210</v>
+        <v>30950</v>
       </c>
       <c r="R9" t="n">
-        <v>-64000</v>
+        <v>-85000</v>
       </c>
       <c r="S9" t="n">
-        <v>41000</v>
+        <v>36000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>이재용 로봇손 관련 부품(엑츄에이터) 시장 신규 진입 소식. 3만원대 돌파 시 추가 상승 기대.</t>
+          <t>사상 최대 실적 발표 및 TC 본더 매출 본격화 기반 상승 전망. 공매도 세력과의 갈등.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['로봇손', '엑츄에이터', '휴머노이드']</t>
+          <t>['실적', 'TC 본더', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>489790</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>양지사</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6900</v>
+        <v>29000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+3.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-0.36</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="H10" t="n">
-        <v>0.85</v>
+        <v>4.69</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6640</v>
+        <v>28050</v>
       </c>
       <c r="K10" t="n">
-        <v>7210</v>
+        <v>27850</v>
       </c>
       <c r="L10" t="n">
-        <v>7500</v>
+        <v>30400</v>
       </c>
       <c r="M10" t="n">
-        <v>6730</v>
+        <v>27650</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9</v>
+        <v>5.05</v>
       </c>
       <c r="O10" t="n">
-        <v>27145224985</v>
+        <v>96001665875</v>
       </c>
       <c r="P10" t="n">
-        <v>9820</v>
+        <v>50600</v>
       </c>
       <c r="Q10" t="n">
-        <v>4000</v>
+        <v>13210</v>
       </c>
       <c r="R10" t="n">
-        <v>-46000</v>
+        <v>-64000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>41000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 시장 흐름에 따른 양지사 급등 언급. 594억 규모 공급 계약 확인 및 유통 물량 관련 논의.</t>
+          <t>로봇 관련 기대감 속 3만원 돌파 시도. 정밀 엑추에이터 시장 진입 뉴스 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공급계약', '테마주', '유통물량']</t>
+          <t>['로봇', '엑추에이터', '반도체']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>030960</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15440</v>
+        <v>4170</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.9</v>
+        <v>-0.77</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
-        <v>231</v>
+        <v>111</v>
       </c>
       <c r="H11" t="n">
-        <v>7.15</v>
+        <v>1.43</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14980</v>
+        <v>4040</v>
       </c>
       <c r="K11" t="n">
-        <v>14980</v>
+        <v>3925</v>
       </c>
       <c r="L11" t="n">
-        <v>16150</v>
+        <v>4265</v>
       </c>
       <c r="M11" t="n">
-        <v>14610</v>
+        <v>3880</v>
       </c>
       <c r="N11" t="n">
-        <v>8.050000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
-        <v>38370181735</v>
+        <v>58794798225</v>
       </c>
       <c r="P11" t="n">
-        <v>49800</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>8180</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>114000</v>
+        <v>426000</v>
       </c>
       <c r="S11" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>유방암 위험 예측 솔루션 '루닛 인사이트 리스크' 미 FDA 승인 신청. AI 신약개발 관련 높은 기대감.</t>
+          <t>상승 기대감과 함께 급등 가능성 언급. 외국인 및 프로그램 매수세 확인되나, '개잡주'라는 부정적 표현도 혼재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI 신약개발', 'FDA 승인', '유방암']</t>
+          <t>['급등 기대', '외국인 매수', '개잡주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>서울바이오시스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8840</v>
+        <v>15390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.03%</t>
+          <t>'+2.74%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.9</v>
       </c>
       <c r="E12" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="H12" t="n">
-        <v>2.67</v>
+        <v>7.15</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>8580</v>
+        <v>14980</v>
       </c>
       <c r="K12" t="n">
-        <v>11090</v>
+        <v>14980</v>
       </c>
       <c r="L12" t="n">
-        <v>11150</v>
+        <v>16150</v>
       </c>
       <c r="M12" t="n">
-        <v>8400</v>
+        <v>14610</v>
       </c>
       <c r="N12" t="n">
-        <v>2.66</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>23371637505</v>
+        <v>39078125230</v>
       </c>
       <c r="P12" t="n">
-        <v>19270</v>
+        <v>49800</v>
       </c>
       <c r="Q12" t="n">
-        <v>2135</v>
+        <v>8180</v>
       </c>
       <c r="R12" t="n">
-        <v>-341000</v>
+        <v>114000</v>
       </c>
       <c r="S12" t="n">
-        <v>-2000</v>
+        <v>26000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>서울반도체와의 비교 및 영업이익 역전 기대. 내년 조단위 매출 및 광통신 사업 확장 전망.</t>
+          <t>유방암 위험 예측 솔루션 FDA 승인 신청 및 AI 신약개발 기대감. 5,000억 원 가치 평가.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '영업이익', '매출']</t>
+          <t>['AI 신약개발', 'FDA 승인', '암 진단']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>092190</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>서울바이오시스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15870</v>
+        <v>8690</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.95%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="H13" t="n">
-        <v>28.13</v>
+        <v>2.67</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>15720</v>
+        <v>8580</v>
       </c>
       <c r="K13" t="n">
-        <v>15420</v>
+        <v>11090</v>
       </c>
       <c r="L13" t="n">
-        <v>16050</v>
+        <v>11150</v>
       </c>
       <c r="M13" t="n">
-        <v>15320</v>
+        <v>8400</v>
       </c>
       <c r="N13" t="n">
-        <v>28.07</v>
+        <v>2.66</v>
       </c>
       <c r="O13" t="n">
-        <v>29609593580</v>
+        <v>24262504685</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>19270</v>
       </c>
       <c r="Q13" t="n">
-        <v>15320</v>
+        <v>2135</v>
       </c>
       <c r="R13" t="n">
-        <v>231000</v>
+        <v>-341000</v>
       </c>
       <c r="S13" t="n">
-        <v>14000</v>
+        <v>-2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 조선주 강세와 비교하며 조선 섹터 기회 언급. 증권사 리포트 긍정적 전망. 대규모 수주 기대.</t>
+          <t>서울반도체와 동반 상승 기대. 광통신 사업 연계 및 매출 조 단위 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['조선주', '수주 기대', '증권사 리포트']</t>
+          <t>['광통신', '신기술', '매출']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>092190</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61100</v>
+        <v>15790</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.71%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G14" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="H14" t="n">
-        <v>41.76</v>
+        <v>28.13</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>62800</v>
+        <v>15720</v>
       </c>
       <c r="K14" t="n">
-        <v>62300</v>
+        <v>15420</v>
       </c>
       <c r="L14" t="n">
-        <v>62800</v>
+        <v>16050</v>
       </c>
       <c r="M14" t="n">
-        <v>60700</v>
+        <v>15320</v>
       </c>
       <c r="N14" t="n">
-        <v>41.55</v>
+        <v>28.07</v>
       </c>
       <c r="O14" t="n">
-        <v>51416847700</v>
+        <v>31207451635</v>
       </c>
       <c r="P14" t="n">
-        <v>67300</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>23150</v>
+        <v>15320</v>
       </c>
       <c r="R14" t="n">
-        <v>69000</v>
+        <v>231000</v>
       </c>
       <c r="S14" t="n">
-        <v>-10000</v>
+        <v>14000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반도체 시장과 대비되는 긍정적 전망. 자사주 취득, 중동 대규모 수주 공시 기대감. 외인 순매수 긍정적 신호.</t>
+          <t>미국 조선주 강세와 비교하며 조선 섹터 기회 언급. 증권사 리포트 긍정적 전망. 대규모 수주 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 취득', '수주 공시', '외국인']</t>
+          <t>['조선주', '수주 기대', '증권사 리포트']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54500</v>
+        <v>7320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.88%</t>
+          <t>'-1.74%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E15" t="n">
-        <v>214</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="G15" t="n">
-        <v>695</v>
+        <v>112</v>
       </c>
       <c r="H15" t="n">
-        <v>22.14</v>
+        <v>25.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>56700</v>
+        <v>7450</v>
       </c>
       <c r="K15" t="n">
-        <v>55500</v>
+        <v>7350</v>
       </c>
       <c r="L15" t="n">
-        <v>55900</v>
+        <v>7570</v>
       </c>
       <c r="M15" t="n">
-        <v>54000</v>
+        <v>7290</v>
       </c>
       <c r="N15" t="n">
-        <v>22.34</v>
+        <v>25.32</v>
       </c>
       <c r="O15" t="n">
-        <v>46214269300</v>
+        <v>6339302335</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>53400</v>
+        <v>7010</v>
       </c>
       <c r="R15" t="n">
-        <v>-85000</v>
+        <v>-24000</v>
       </c>
       <c r="S15" t="n">
-        <v>-58000</v>
+        <v>-2000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 전망. 체코 원전 사업 관련 비판과 함께 원전주 상승 가능성 언급. 실적과 무관한 주가 움직임에 대한 불만.</t>
+          <t>임원 자사주 매입 및 칩 인플레이션 해소 관련 긍정적 언급. 주가 하락 및 노조 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['SMR', '수주', '실적']</t>
+          <t>['자사주 매입', '칩 인플레이션', '노조']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11080</v>
+        <v>60900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.65%</t>
+          <t>'-3.03%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="E16" t="n">
-        <v>264</v>
+        <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>137</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>889</v>
+        <v>229</v>
       </c>
       <c r="H16" t="n">
-        <v>9.73</v>
+        <v>41.76</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,38 +1883,38 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>11620</v>
+        <v>62800</v>
       </c>
       <c r="K16" t="n">
-        <v>11300</v>
+        <v>62300</v>
       </c>
       <c r="L16" t="n">
-        <v>11470</v>
+        <v>62800</v>
       </c>
       <c r="M16" t="n">
-        <v>10960</v>
+        <v>60700</v>
       </c>
       <c r="N16" t="n">
-        <v>9.6</v>
+        <v>41.55</v>
       </c>
       <c r="O16" t="n">
-        <v>35099989245</v>
+        <v>53634330050</v>
       </c>
       <c r="P16" t="n">
-        <v>40350</v>
+        <v>67300</v>
       </c>
       <c r="Q16" t="n">
-        <v>3320</v>
+        <v>23150</v>
       </c>
       <c r="R16" t="n">
-        <v>101000</v>
+        <v>69000</v>
       </c>
       <c r="S16" t="n">
-        <v>-32000</v>
+        <v>-10000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>원전, 가덕도 관련 정부 정책 수혜 기대. 공매도 금지 조치 언급. 재건 사업 전망도 긍정적 요인으로 작용.</t>
+          <t>자사주 취득 및 중동 대규모 수주 공시 기대감. 외인/프매의 매수세와 함께 긍정적 전망이 일부 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '가덕도', '공매도 금지']</t>
+          <t>['자사주 취득', '수주 공시', '외인 매수']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>218500</v>
+        <v>54100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.82%</t>
+          <t>'-4.59%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.02</v>
+        <v>-0.2</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>219</v>
       </c>
       <c r="F17" t="n">
-        <v>524</v>
+        <v>151</v>
       </c>
       <c r="G17" t="n">
-        <v>1230</v>
+        <v>743</v>
       </c>
       <c r="H17" t="n">
-        <v>46.17</v>
+        <v>22.14</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>232000</v>
+        <v>56700</v>
       </c>
       <c r="K17" t="n">
-        <v>223500</v>
+        <v>55500</v>
       </c>
       <c r="L17" t="n">
-        <v>229500</v>
+        <v>55900</v>
       </c>
       <c r="M17" t="n">
-        <v>218000</v>
+        <v>54000</v>
       </c>
       <c r="N17" t="n">
-        <v>46.19</v>
+        <v>22.34</v>
       </c>
       <c r="O17" t="n">
-        <v>1533968500500</v>
+        <v>50249210600</v>
       </c>
       <c r="P17" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>94500</v>
+        <v>53400</v>
       </c>
       <c r="R17" t="n">
-        <v>1338000</v>
+        <v>-85000</v>
       </c>
       <c r="S17" t="n">
-        <v>-249000</v>
+        <v>-58000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>이재용 증여세, 노조 행동, 정치적 리스크 등 부정적 요인 언급. 하지만 구체적인 실적이나 공시 기반 분석은 부족.</t>
+          <t>미국 뉴스케일파워 SMR 원자로 수주 및 실적 개선 전망. 체코 원전 사업 관련 비판과 함께 원전주 상승 가능성 언급. 실적과 무관한 주가 움직임에 대한 불만.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['이재용', '노조', '리스크']</t>
+          <t>['SMR', '수주', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22150</v>
+        <v>10940</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.14%</t>
+          <t>'-5.85%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.63</v>
+        <v>0.13</v>
       </c>
       <c r="E18" t="n">
-        <v>174</v>
+        <v>271</v>
       </c>
       <c r="F18" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G18" t="n">
-        <v>411</v>
+        <v>913</v>
       </c>
       <c r="H18" t="n">
-        <v>11.6</v>
+        <v>9.73</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>23600</v>
+        <v>11620</v>
       </c>
       <c r="K18" t="n">
-        <v>22650</v>
+        <v>11300</v>
       </c>
       <c r="L18" t="n">
-        <v>22700</v>
+        <v>11470</v>
       </c>
       <c r="M18" t="n">
-        <v>21100</v>
+        <v>10920</v>
       </c>
       <c r="N18" t="n">
-        <v>12.23</v>
+        <v>9.6</v>
       </c>
       <c r="O18" t="n">
-        <v>58996779775</v>
+        <v>37860454975</v>
       </c>
       <c r="P18" t="n">
-        <v>59300</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>21100</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-481000</v>
+        <v>101000</v>
       </c>
       <c r="S18" t="n">
-        <v>-144000</v>
+        <v>-32000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>태양광 사업 관련 긍정적 뉴스 언급 있으나, 주가 하락세에 대한 우려가 지배적. 주가 누르기 의혹 제기.</t>
+          <t>원전, 가덕도 관련 정부 정책 수혜 기대. 공매도 금지 조치 언급. 재건 사업 전망도 긍정적 요인으로 작용.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['태양광', '주가 하락', '주가 조작']</t>
+          <t>['원전', '가덕도', '공매도 금지']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14030</v>
+        <v>216750</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.65%</t>
+          <t>'-6.57%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>78</v>
+        <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>44</v>
+        <v>527</v>
       </c>
       <c r="G19" t="n">
-        <v>260</v>
+        <v>1197</v>
       </c>
       <c r="H19" t="n">
-        <v>3.13</v>
+        <v>46.17</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>15030</v>
+        <v>232000</v>
       </c>
       <c r="K19" t="n">
-        <v>14500</v>
+        <v>223500</v>
       </c>
       <c r="L19" t="n">
-        <v>14570</v>
+        <v>229500</v>
       </c>
       <c r="M19" t="n">
-        <v>13920</v>
+        <v>216500</v>
       </c>
       <c r="N19" t="n">
-        <v>3.33</v>
+        <v>46.19</v>
       </c>
       <c r="O19" t="n">
-        <v>28997246500</v>
+        <v>1660948821750</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q19" t="n">
-        <v>1830</v>
+        <v>94500</v>
       </c>
       <c r="R19" t="n">
-        <v>8000</v>
+        <v>1338000</v>
       </c>
       <c r="S19" t="n">
-        <v>-9000</v>
+        <v>-249000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 주식 동반 상승 및 루닛 연기금 매수 언급. 3만 전고점까지 홀딩 전망.</t>
+          <t>정치적 이슈와 연관된 부정적 언급이 다수. 주주환원 정책 발표 기대감도 있으나, 불확실성 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '연기금', '전고점']</t>
+          <t>['주주환원', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1401000</v>
+        <v>21850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-8.19%</t>
+          <t>'-7.42%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.06</v>
+        <v>-0.63</v>
       </c>
       <c r="E20" t="n">
-        <v>800</v>
+        <v>176</v>
       </c>
       <c r="F20" t="n">
-        <v>536</v>
+        <v>136</v>
       </c>
       <c r="G20" t="n">
-        <v>1114</v>
+        <v>421</v>
       </c>
       <c r="H20" t="n">
-        <v>48.72</v>
+        <v>11.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,51 +2251,51 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1526000</v>
+        <v>23600</v>
       </c>
       <c r="K20" t="n">
-        <v>1444000</v>
+        <v>22650</v>
       </c>
       <c r="L20" t="n">
-        <v>1446000</v>
+        <v>22700</v>
       </c>
       <c r="M20" t="n">
-        <v>1387000</v>
+        <v>21100</v>
       </c>
       <c r="N20" t="n">
-        <v>48.66</v>
+        <v>12.23</v>
       </c>
       <c r="O20" t="n">
-        <v>1967930374000</v>
+        <v>61308844450</v>
       </c>
       <c r="P20" t="n">
-        <v>2987000</v>
+        <v>59300</v>
       </c>
       <c r="Q20" t="n">
-        <v>501000</v>
+        <v>21100</v>
       </c>
       <c r="R20" t="n">
-        <v>-65000</v>
+        <v>-481000</v>
       </c>
       <c r="S20" t="n">
-        <v>-80000</v>
+        <v>-144000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>정치적 이슈와 함께 전반적인 시장 하락세에 대한 부정적 전망. 외국인 투자자 관점 언급. 단기 차익 실현 권장.</t>
+          <t>태양광 사업 관련 긍정적 뉴스 언급 있으나, 주가 하락세에 대한 우려가 지배적. 주가 누르기 의혹 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['시장 하락', '외국인', '단기 매매']</t>
+          <t>['태양광', '주가 하락', '주가 조작']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,90 +2304,90 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>서산</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7220</v>
+        <v>169700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.61%</t>
+          <t>'-7.72%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G21" t="n">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="H21" t="n">
-        <v>0.39</v>
+        <v>74.87</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7900</v>
+        <v>183900</v>
       </c>
       <c r="K21" t="n">
-        <v>7790</v>
+        <v>176800</v>
       </c>
       <c r="L21" t="n">
-        <v>8130</v>
+        <v>179000</v>
       </c>
       <c r="M21" t="n">
-        <v>7150</v>
+        <v>169600</v>
       </c>
       <c r="N21" t="n">
-        <v>0.42</v>
+        <v>75</v>
       </c>
       <c r="O21" t="n">
-        <v>13260798115</v>
+        <v>361810855350</v>
       </c>
       <c r="P21" t="n">
-        <v>10300</v>
+        <v>243500</v>
       </c>
       <c r="Q21" t="n">
-        <v>952</v>
+        <v>71000</v>
       </c>
       <c r="R21" t="n">
-        <v>-11000</v>
+        <v>-139000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
+          <t>주가 조작 및 증여세 관련 부정적 언급과 함께 시장 대폭락에 대한 우려가 존재. 우선주 소각 및 반등 기대도 일부.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['공급계약', '재료', '주가']</t>
+          <t>['주가 조작', '증여세', '우선주 소각']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,77 +2396,77 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>079650</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>118400</v>
+        <v>13820</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-14.33%</t>
+          <t>'-8.05%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G22" t="n">
-        <v>182</v>
+        <v>271</v>
       </c>
       <c r="H22" t="n">
-        <v>14.2</v>
+        <v>3.13</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>138200</v>
+        <v>15030</v>
       </c>
       <c r="K22" t="n">
-        <v>132600</v>
+        <v>14500</v>
       </c>
       <c r="L22" t="n">
-        <v>132900</v>
+        <v>14570</v>
       </c>
       <c r="M22" t="n">
-        <v>118000</v>
+        <v>13820</v>
       </c>
       <c r="N22" t="n">
-        <v>14.46</v>
+        <v>3.33</v>
       </c>
       <c r="O22" t="n">
-        <v>94826762950</v>
+        <v>31284235310</v>
       </c>
       <c r="P22" t="n">
-        <v>198000</v>
+        <v>31500</v>
       </c>
       <c r="Q22" t="n">
-        <v>36450</v>
+        <v>1830</v>
       </c>
       <c r="R22" t="n">
-        <v>-162000</v>
+        <v>8000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>반도체 섹터 전반의 하락세 속에 급락. 실적에 대한 기대감 있으나, 주가 하락폭이 커 투자자 불안감 고조.</t>
+          <t>미국 광통신 주식 동반 상승 및 루닛 연기금 매수 언급. 3만 전고점까지 홀딩 전망.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['반도체', '실적', '주가 하락']</t>
+          <t>['광통신', '연기금', '전고점']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,90 +2488,90 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13510</v>
+        <v>1384000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-20.53%</t>
+          <t>'-9.31%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="E23" t="n">
-        <v>133</v>
+        <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>56</v>
+        <v>541</v>
       </c>
       <c r="G23" t="n">
-        <v>106</v>
+        <v>1213</v>
       </c>
       <c r="H23" t="n">
-        <v>0.66</v>
+        <v>48.72</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>17000</v>
+        <v>1526000</v>
       </c>
       <c r="K23" t="n">
-        <v>14000</v>
+        <v>1444000</v>
       </c>
       <c r="L23" t="n">
-        <v>14900</v>
+        <v>1446000</v>
       </c>
       <c r="M23" t="n">
-        <v>13260</v>
+        <v>1381000</v>
       </c>
       <c r="N23" t="n">
-        <v>0.65</v>
+        <v>48.66</v>
       </c>
       <c r="O23" t="n">
-        <v>26107844565</v>
+        <v>2085821572000</v>
       </c>
       <c r="P23" t="n">
-        <v>28800</v>
+        <v>2987000</v>
       </c>
       <c r="Q23" t="n">
-        <v>11550</v>
+        <v>501000</v>
       </c>
       <c r="R23" t="n">
-        <v>-7000</v>
+        <v>-65000</v>
       </c>
       <c r="S23" t="n">
-        <v>-150000</v>
+        <v>-80000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>보호예수 해제 및 마이크론 퀠테스트 통과 관련 기대감에도 불구하고 주가 하락. ASML 장비 수주 공시 시 급등 가능성 언급.</t>
+          <t>시장 폭락에 대한 부정적 언급이 지배적이며, 정치적 요인 및 개미 투자 실패에 대한 불만이 많음.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['보호예수', '마이크론', 'ASML']</t>
+          <t>['시장 폭락', '정치적 요인', '개미 투자']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10730</v>
+        <v>7150</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-28.47%</t>
+          <t>'-9.49%</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E24" t="n">
+        <v>49</v>
+      </c>
+      <c r="F24" t="n">
+        <v>24</v>
+      </c>
+      <c r="G24" t="n">
+        <v>87</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>7900</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7790</v>
+      </c>
+      <c r="L24" t="n">
+        <v>8130</v>
+      </c>
+      <c r="M24" t="n">
+        <v>7100</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="O24" t="n">
+        <v>13708464955</v>
+      </c>
+      <c r="P24" t="n">
+        <v>10300</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>952</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-11000</v>
+      </c>
+      <c r="S24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
-        <v>270</v>
-      </c>
-      <c r="F24" t="n">
-        <v>131</v>
-      </c>
-      <c r="G24" t="n">
-        <v>410</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>MarketType.KOSDAQ</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K24" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L24" t="n">
-        <v>12700</v>
-      </c>
-      <c r="M24" t="n">
-        <v>9790</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>88084018335</v>
-      </c>
-      <c r="P24" t="n">
-        <v>12700</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>9790</v>
-      </c>
-      <c r="R24" t="n">
-        <v>-40000</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-168000</v>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>미국 유럽 실내골프 대회 개최 등 대중화 초입 단계 언급. 상장 직후 하한가에 대한 주관사 사기 의혹 제기.</t>
+          <t>서산, 594억 공급 계약 재료를 바탕으로 한 긍정적 전망. 다만, 시장 전체 하락세 및 개미 투자자 심리 불안감 존재.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['실내골프', '대중화', '상장']</t>
+          <t>['공급계약', '재료', '주가']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,86 +2672,86 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>439270</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>벡트로보틱스</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1831</v>
+        <v>117300</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-28.89%</t>
+          <t>'-15.12%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.45</v>
+        <v>-0.26</v>
       </c>
       <c r="E25" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="G25" t="n">
-        <v>25</v>
+        <v>204</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>14.2</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2575</v>
+        <v>138200</v>
       </c>
       <c r="K25" t="n">
-        <v>1960</v>
+        <v>132600</v>
       </c>
       <c r="L25" t="n">
-        <v>2005</v>
+        <v>132900</v>
       </c>
       <c r="M25" t="n">
-        <v>1811</v>
+        <v>117000</v>
       </c>
       <c r="N25" t="n">
-        <v>3.35</v>
+        <v>14.46</v>
       </c>
       <c r="O25" t="n">
-        <v>6039476906</v>
+        <v>102394208500</v>
       </c>
       <c r="P25" t="n">
-        <v>5700</v>
+        <v>198000</v>
       </c>
       <c r="Q25" t="n">
-        <v>1401</v>
+        <v>36450</v>
       </c>
       <c r="R25" t="n">
-        <v>219000</v>
+        <v>-162000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>연이은 하한가 및 거래정지 가능성 언급. 대표이사가 투자조합이며 실적 부진으로 인한 하락세 지적.</t>
+          <t>실적 발표 전 급락에도 불구하고, SK하이닉스 소부장 물량 확대 뉴스 및 실적 기대감으로 인한 저점 매수 의견 존재. 그러나 명확한 공시나 실적 근거 부족 및 급격한 주가 하락에 대한 불안감 혼재.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['거래정지', '실적부진', '투자조합']</t>
+          <t>['실적', '반도체', '수급']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2764,7 +2764,283 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
+          <t>353200</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>멜콘</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>13390</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>'-21.24%</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" t="n">
+        <v>143</v>
+      </c>
+      <c r="F26" t="n">
+        <v>58</v>
+      </c>
+      <c r="G26" t="n">
+        <v>110</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>17000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14900</v>
+      </c>
+      <c r="M26" t="n">
+        <v>13260</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O26" t="n">
+        <v>26978312375</v>
+      </c>
+      <c r="P26" t="n">
+        <v>28800</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>11550</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-7000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-150000</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>보호예수 물량 해제 후 변동성 확대. 마이크론 퀄테스트 통과 사실 기반 반등 기대.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>['보호예수', '퀄테스트', '반도체']</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>179880</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>벡트로보틱스</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1861</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>'-27.73%</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E27" t="n">
+        <v>48</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G27" t="n">
+        <v>25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>2575</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1960</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2005</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1811</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6130840174</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5700</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1401</v>
+      </c>
+      <c r="R27" t="n">
+        <v>219000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>연이은 하한가 기록. 투자자 불안감 고조 및 상장폐지 우려 제기.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>['하한가', '유상증자', '상장폐지']</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
           <t>457600</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10430</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>'-30.47%</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>295</v>
+      </c>
+      <c r="F28" t="n">
+        <v>142</v>
+      </c>
+      <c r="G28" t="n">
+        <v>451</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K28" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M28" t="n">
+        <v>9790</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>90827736930</v>
+      </c>
+      <c r="P28" t="n">
+        <v>12700</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>9790</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-168000</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>미국 유럽 실내골프대회 및 대중화 관련 긍정적 전망. 작년 매출 및 영업이익 수치 언급. 주포의 움직임에 대한 기대.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>['골프주', '매출', '주포']</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>439270</t>
         </is>
       </c>
     </row>
